--- a/Shablon/MSO9404A.xlsx
+++ b/Shablon/MSO9404A.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="740">
   <si>
     <t>Установленый коэффицент отклонения, мВ/дел</t>
   </si>
@@ -1135,13 +1135,6 @@
   </si>
   <si>
     <t>канал 4</t>
-  </si>
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"
-СГМетр, лаборатория средств электрорадиотехнических измерений
-125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23
-Уникальный номер об аккредитации в реестре аккредитованных лиц № РОСС СОБ 3.00231.2014
-Тел. +7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
   </si>
   <si>
     <t>_temp</t>
@@ -3713,32 +3706,24 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3753,13 +3738,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3772,24 +3750,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3819,20 +3781,51 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="11" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -4158,23 +4151,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="2" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
+      <c r="A1" s="61"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4196,23 +4187,23 @@
       <c r="P2" s="3"/>
     </row>
     <row r="3" spans="1:16" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
+      <c r="A3" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
       <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16" s="2" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4237,7 +4228,7 @@
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4274,23 +4265,23 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
+      <c r="A7" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4350,16 +4341,16 @@
       <c r="P10" s="3"/>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="58" t="s">
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="52"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -4372,16 +4363,16 @@
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="61"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="54"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -4394,16 +4385,16 @@
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="61"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="54"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -4416,16 +4407,16 @@
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="61"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="54"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -4456,24 +4447,24 @@
       <c r="P15" s="3"/>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
+      <c r="A16" s="64" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
@@ -4495,7 +4486,7 @@
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -4533,7 +4524,7 @@
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -4608,23 +4599,23 @@
       <c r="P23" s="3"/>
     </row>
     <row r="24" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="55"/>
       <c r="P24" s="15"/>
     </row>
     <row r="25" spans="1:16" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -4646,2481 +4637,2481 @@
       <c r="P25" s="15"/>
     </row>
     <row r="26" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38" t="s">
+      <c r="C26" s="47"/>
+      <c r="D26" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38" t="s">
+      <c r="F26" s="47"/>
+      <c r="G26" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38" t="s">
+      <c r="H26" s="47"/>
+      <c r="I26" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38" t="s">
+      <c r="J26" s="47"/>
+      <c r="K26" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38" t="s">
+      <c r="L26" s="47"/>
+      <c r="M26" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38" t="s">
+      <c r="N26" s="47"/>
+      <c r="O26" s="47" t="s">
         <v>37</v>
       </c>
       <c r="P26" s="15"/>
     </row>
     <row r="27" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
+      <c r="A27" s="45"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="47"/>
       <c r="P27" s="15"/>
     </row>
     <row r="28" spans="1:16" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="49"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="47"/>
       <c r="P28" s="15"/>
     </row>
     <row r="29" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="35">
+      <c r="A29" s="39">
         <v>1</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="35"/>
+      <c r="C29" s="39"/>
       <c r="D29" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="40" t="s">
+        <v>607</v>
+      </c>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40" t="s">
         <v>608</v>
       </c>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45" t="s">
+      <c r="H29" s="40"/>
+      <c r="I29" s="40" t="s">
         <v>609</v>
       </c>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45" t="s">
+      <c r="J29" s="40"/>
+      <c r="K29" s="40" t="s">
         <v>610</v>
       </c>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45" t="s">
-        <v>611</v>
-      </c>
-      <c r="L29" s="45"/>
-      <c r="M29" s="46" t="e">
+      <c r="L29" s="40"/>
+      <c r="M29" s="60" t="e">
         <f>((I29-K29)/(E29-G29)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N29" s="46"/>
-      <c r="O29" s="35" t="s">
+      <c r="N29" s="60"/>
+      <c r="O29" s="39" t="s">
         <v>38</v>
       </c>
       <c r="P29" s="15"/>
     </row>
     <row r="30" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="35"/>
-      <c r="B30" s="35" t="s">
+      <c r="A30" s="39"/>
+      <c r="B30" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="35"/>
+      <c r="C30" s="39"/>
       <c r="D30" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="45" t="s">
+      <c r="E30" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45" t="s">
+      <c r="H30" s="40"/>
+      <c r="I30" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45" t="s">
+      <c r="J30" s="40"/>
+      <c r="K30" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="L30" s="45"/>
-      <c r="M30" s="46" t="e">
+      <c r="L30" s="40"/>
+      <c r="M30" s="60" t="e">
         <f t="shared" ref="M30:M35" si="0">((I30-K30)/(E30-G30)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N30" s="46"/>
-      <c r="O30" s="35"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="39"/>
       <c r="P30" s="15"/>
     </row>
     <row r="31" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="35"/>
-      <c r="B31" s="35" t="s">
+      <c r="A31" s="39"/>
+      <c r="B31" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="35"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="45" t="s">
+      <c r="E31" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45" t="s">
+      <c r="H31" s="40"/>
+      <c r="I31" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45" t="s">
+      <c r="J31" s="40"/>
+      <c r="K31" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="L31" s="45"/>
-      <c r="M31" s="46" t="e">
+      <c r="L31" s="40"/>
+      <c r="M31" s="60" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N31" s="46"/>
-      <c r="O31" s="35"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="39"/>
       <c r="P31" s="15"/>
     </row>
     <row r="32" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="35"/>
-      <c r="B32" s="35" t="s">
+      <c r="A32" s="39"/>
+      <c r="B32" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="35"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45" t="s">
+      <c r="H32" s="40"/>
+      <c r="I32" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45" t="s">
+      <c r="J32" s="40"/>
+      <c r="K32" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="L32" s="45"/>
-      <c r="M32" s="46" t="e">
+      <c r="L32" s="40"/>
+      <c r="M32" s="60" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N32" s="46"/>
-      <c r="O32" s="35"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="39"/>
       <c r="P32" s="15"/>
     </row>
     <row r="33" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="35"/>
-      <c r="B33" s="35" t="s">
+      <c r="A33" s="39"/>
+      <c r="B33" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="35"/>
+      <c r="C33" s="39"/>
       <c r="D33" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="45" t="s">
+      <c r="E33" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45" t="s">
+      <c r="H33" s="40"/>
+      <c r="I33" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45" t="s">
+      <c r="J33" s="40"/>
+      <c r="K33" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="L33" s="45"/>
-      <c r="M33" s="46" t="e">
+      <c r="L33" s="40"/>
+      <c r="M33" s="60" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N33" s="46"/>
-      <c r="O33" s="35"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="39"/>
       <c r="P33" s="15"/>
     </row>
     <row r="34" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35" t="s">
+      <c r="A34" s="39"/>
+      <c r="B34" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="35"/>
+      <c r="C34" s="39"/>
       <c r="D34" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="45" t="s">
+      <c r="E34" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45" t="s">
+      <c r="H34" s="40"/>
+      <c r="I34" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45" t="s">
+      <c r="J34" s="40"/>
+      <c r="K34" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="L34" s="45"/>
-      <c r="M34" s="46" t="e">
+      <c r="L34" s="40"/>
+      <c r="M34" s="60" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N34" s="46"/>
-      <c r="O34" s="35"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="39"/>
       <c r="P34" s="15"/>
     </row>
     <row r="35" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A35" s="35"/>
-      <c r="B35" s="35" t="s">
+      <c r="A35" s="39"/>
+      <c r="B35" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="35"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="45" t="s">
+      <c r="E35" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45" t="s">
+      <c r="H35" s="40"/>
+      <c r="I35" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45" t="s">
+      <c r="J35" s="40"/>
+      <c r="K35" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="L35" s="45"/>
-      <c r="M35" s="46" t="e">
+      <c r="L35" s="40"/>
+      <c r="M35" s="60" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N35" s="46"/>
-      <c r="O35" s="35"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="39"/>
       <c r="P35" s="15"/>
     </row>
     <row r="36" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A36" s="35"/>
-      <c r="B36" s="35" t="s">
+      <c r="A36" s="39"/>
+      <c r="B36" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="35"/>
+      <c r="C36" s="39"/>
       <c r="D36" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45" t="s">
+      <c r="H36" s="40"/>
+      <c r="I36" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45" t="s">
+      <c r="J36" s="40"/>
+      <c r="K36" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="L36" s="45"/>
-      <c r="M36" s="46" t="e">
+      <c r="L36" s="40"/>
+      <c r="M36" s="60" t="e">
         <f>((I36-K36)/(E36-G36)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N36" s="46"/>
-      <c r="O36" s="35"/>
+      <c r="N36" s="60"/>
+      <c r="O36" s="39"/>
       <c r="P36" s="15"/>
     </row>
     <row r="37" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="47" t="s">
+      <c r="A37" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38" t="s">
+      <c r="C37" s="47"/>
+      <c r="D37" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E37" s="38" t="s">
+      <c r="E37" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38" t="s">
+      <c r="F37" s="47"/>
+      <c r="G37" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38" t="s">
+      <c r="H37" s="47"/>
+      <c r="I37" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="38"/>
-      <c r="K37" s="38" t="s">
+      <c r="J37" s="47"/>
+      <c r="K37" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38" t="s">
+      <c r="L37" s="47"/>
+      <c r="M37" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38" t="s">
+      <c r="N37" s="47"/>
+      <c r="O37" s="47" t="s">
         <v>37</v>
       </c>
       <c r="P37" s="15"/>
     </row>
     <row r="38" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="48"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="38"/>
+      <c r="A38" s="45"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="47"/>
+      <c r="L38" s="47"/>
+      <c r="M38" s="47"/>
+      <c r="N38" s="47"/>
+      <c r="O38" s="47"/>
       <c r="P38" s="15"/>
     </row>
     <row r="39" spans="1:16" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="49"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="38"/>
+      <c r="A39" s="46"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="47"/>
+      <c r="J39" s="47"/>
+      <c r="K39" s="47"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="47"/>
+      <c r="N39" s="47"/>
+      <c r="O39" s="47"/>
       <c r="P39" s="15"/>
     </row>
     <row r="40" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="35">
+      <c r="A40" s="39">
         <v>1</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="35"/>
+      <c r="C40" s="39"/>
       <c r="D40" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="45" t="s">
+      <c r="E40" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45" t="s">
+      <c r="H40" s="40"/>
+      <c r="I40" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45" t="s">
+      <c r="J40" s="40"/>
+      <c r="K40" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="L40" s="45"/>
-      <c r="M40" s="46" t="e">
+      <c r="L40" s="40"/>
+      <c r="M40" s="60" t="e">
         <f>((I40-K40)/(E40-G40)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N40" s="46"/>
-      <c r="O40" s="35" t="s">
+      <c r="N40" s="60"/>
+      <c r="O40" s="39" t="s">
         <v>38</v>
       </c>
       <c r="P40" s="15"/>
     </row>
     <row r="41" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="35"/>
-      <c r="B41" s="35" t="s">
+      <c r="A41" s="39"/>
+      <c r="B41" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="35"/>
+      <c r="C41" s="39"/>
       <c r="D41" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E41" s="45" t="s">
+      <c r="E41" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45" t="s">
+      <c r="H41" s="40"/>
+      <c r="I41" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45" t="s">
+      <c r="J41" s="40"/>
+      <c r="K41" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="J41" s="45"/>
-      <c r="K41" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="L41" s="45"/>
-      <c r="M41" s="46" t="e">
+      <c r="L41" s="40"/>
+      <c r="M41" s="60" t="e">
         <f>((I41-K41)/(E41-G41)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N41" s="46"/>
-      <c r="O41" s="35"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="39"/>
       <c r="P41" s="15"/>
     </row>
     <row r="42" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="35"/>
-      <c r="B42" s="35" t="s">
+      <c r="A42" s="39"/>
+      <c r="B42" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="35"/>
+      <c r="C42" s="39"/>
       <c r="D42" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="40" t="s">
+        <v>611</v>
+      </c>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40" t="s">
         <v>612</v>
       </c>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45" t="s">
+      <c r="H42" s="40"/>
+      <c r="I42" s="40" t="s">
         <v>613</v>
       </c>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45" t="s">
+      <c r="J42" s="40"/>
+      <c r="K42" s="40" t="s">
         <v>614</v>
       </c>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45" t="s">
-        <v>615</v>
-      </c>
-      <c r="L42" s="45"/>
-      <c r="M42" s="46" t="e">
+      <c r="L42" s="40"/>
+      <c r="M42" s="60" t="e">
         <f t="shared" ref="M42:M47" si="1">((I42-K42)/(E42-G42)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N42" s="46"/>
-      <c r="O42" s="35"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="39"/>
       <c r="P42" s="15"/>
     </row>
     <row r="43" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A43" s="35"/>
-      <c r="B43" s="35" t="s">
+      <c r="A43" s="39"/>
+      <c r="B43" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="35"/>
+      <c r="C43" s="39"/>
       <c r="D43" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="45" t="s">
+      <c r="E43" s="40" t="s">
+        <v>615</v>
+      </c>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40" t="s">
         <v>616</v>
       </c>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45" t="s">
+      <c r="H43" s="40"/>
+      <c r="I43" s="40" t="s">
         <v>617</v>
       </c>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45" t="s">
+      <c r="J43" s="40"/>
+      <c r="K43" s="40" t="s">
         <v>618</v>
       </c>
-      <c r="J43" s="45"/>
-      <c r="K43" s="45" t="s">
-        <v>619</v>
-      </c>
-      <c r="L43" s="45"/>
-      <c r="M43" s="46" t="e">
+      <c r="L43" s="40"/>
+      <c r="M43" s="60" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N43" s="46"/>
-      <c r="O43" s="35"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="39"/>
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="35"/>
-      <c r="B44" s="35" t="s">
+      <c r="A44" s="39"/>
+      <c r="B44" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="35"/>
+      <c r="C44" s="39"/>
       <c r="D44" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E44" s="45" t="s">
+      <c r="E44" s="40" t="s">
+        <v>619</v>
+      </c>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40" t="s">
         <v>620</v>
       </c>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45" t="s">
+      <c r="H44" s="40"/>
+      <c r="I44" s="40" t="s">
         <v>621</v>
       </c>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45" t="s">
+      <c r="J44" s="40"/>
+      <c r="K44" s="40" t="s">
         <v>622</v>
       </c>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45" t="s">
-        <v>623</v>
-      </c>
-      <c r="L44" s="45"/>
-      <c r="M44" s="46" t="e">
+      <c r="L44" s="40"/>
+      <c r="M44" s="60" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N44" s="46"/>
-      <c r="O44" s="35"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="39"/>
       <c r="P44" s="15"/>
     </row>
     <row r="45" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="35"/>
-      <c r="B45" s="35" t="s">
+      <c r="A45" s="39"/>
+      <c r="B45" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="35"/>
+      <c r="C45" s="39"/>
       <c r="D45" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E45" s="45" t="s">
+      <c r="E45" s="40" t="s">
+        <v>623</v>
+      </c>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40" t="s">
         <v>624</v>
       </c>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45" t="s">
+      <c r="H45" s="40"/>
+      <c r="I45" s="40" t="s">
         <v>625</v>
       </c>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45" t="s">
+      <c r="J45" s="40"/>
+      <c r="K45" s="40" t="s">
         <v>626</v>
       </c>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45" t="s">
-        <v>627</v>
-      </c>
-      <c r="L45" s="45"/>
-      <c r="M45" s="46" t="e">
+      <c r="L45" s="40"/>
+      <c r="M45" s="60" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N45" s="46"/>
-      <c r="O45" s="35"/>
+      <c r="N45" s="60"/>
+      <c r="O45" s="39"/>
       <c r="P45" s="15"/>
     </row>
     <row r="46" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A46" s="35"/>
-      <c r="B46" s="35" t="s">
+      <c r="A46" s="39"/>
+      <c r="B46" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="35"/>
+      <c r="C46" s="39"/>
       <c r="D46" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E46" s="45" t="s">
+      <c r="E46" s="40" t="s">
+        <v>627</v>
+      </c>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40" t="s">
         <v>628</v>
       </c>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45" t="s">
+      <c r="H46" s="40"/>
+      <c r="I46" s="40" t="s">
         <v>629</v>
       </c>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45" t="s">
+      <c r="J46" s="40"/>
+      <c r="K46" s="40" t="s">
         <v>630</v>
       </c>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45" t="s">
-        <v>631</v>
-      </c>
-      <c r="L46" s="45"/>
-      <c r="M46" s="46" t="e">
+      <c r="L46" s="40"/>
+      <c r="M46" s="60" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N46" s="46"/>
-      <c r="O46" s="35"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="39"/>
       <c r="P46" s="15"/>
     </row>
     <row r="47" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="35"/>
-      <c r="B47" s="35" t="s">
+      <c r="A47" s="39"/>
+      <c r="B47" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="35"/>
+      <c r="C47" s="39"/>
       <c r="D47" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E47" s="45" t="s">
+      <c r="E47" s="40" t="s">
+        <v>631</v>
+      </c>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40" t="s">
         <v>632</v>
       </c>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45" t="s">
+      <c r="H47" s="40"/>
+      <c r="I47" s="40" t="s">
         <v>633</v>
       </c>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45" t="s">
+      <c r="J47" s="40"/>
+      <c r="K47" s="40" t="s">
         <v>634</v>
       </c>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45" t="s">
-        <v>635</v>
-      </c>
-      <c r="L47" s="45"/>
-      <c r="M47" s="46" t="e">
+      <c r="L47" s="40"/>
+      <c r="M47" s="60" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N47" s="46"/>
-      <c r="O47" s="35"/>
+      <c r="N47" s="60"/>
+      <c r="O47" s="39"/>
       <c r="P47" s="15"/>
     </row>
     <row r="48" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="35"/>
-      <c r="B48" s="35" t="s">
+      <c r="A48" s="39"/>
+      <c r="B48" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="35"/>
+      <c r="C48" s="39"/>
       <c r="D48" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E48" s="45" t="s">
+      <c r="E48" s="40" t="s">
+        <v>635</v>
+      </c>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40" t="s">
         <v>636</v>
       </c>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45" t="s">
+      <c r="H48" s="40"/>
+      <c r="I48" s="40" t="s">
         <v>637</v>
       </c>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45" t="s">
+      <c r="J48" s="40"/>
+      <c r="K48" s="40" t="s">
         <v>638</v>
       </c>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45" t="s">
-        <v>639</v>
-      </c>
-      <c r="L48" s="45"/>
-      <c r="M48" s="46" t="e">
+      <c r="L48" s="40"/>
+      <c r="M48" s="60" t="e">
         <f>((I48-K48)/(E48-G48)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N48" s="46"/>
-      <c r="O48" s="35"/>
+      <c r="N48" s="60"/>
+      <c r="O48" s="39"/>
       <c r="P48" s="15"/>
     </row>
     <row r="49" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="35">
+      <c r="A49" s="39">
         <v>2</v>
       </c>
-      <c r="B49" s="35" t="s">
+      <c r="B49" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="35"/>
+      <c r="C49" s="39"/>
       <c r="D49" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="40" t="s">
+        <v>639</v>
+      </c>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40" t="s">
         <v>640</v>
       </c>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45" t="s">
+      <c r="H49" s="40"/>
+      <c r="I49" s="40" t="s">
         <v>641</v>
       </c>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45" t="s">
+      <c r="J49" s="40"/>
+      <c r="K49" s="40" t="s">
         <v>642</v>
       </c>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45" t="s">
-        <v>643</v>
-      </c>
-      <c r="L49" s="45"/>
-      <c r="M49" s="46" t="e">
+      <c r="L49" s="40"/>
+      <c r="M49" s="60" t="e">
         <f>((I49-K49)/(E49-G49)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N49" s="46"/>
-      <c r="O49" s="35"/>
+      <c r="N49" s="60"/>
+      <c r="O49" s="39"/>
       <c r="P49" s="15"/>
     </row>
     <row r="50" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="35"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="35"/>
+      <c r="C50" s="39"/>
       <c r="D50" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45" t="s">
+      <c r="H50" s="40"/>
+      <c r="I50" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45" t="s">
+      <c r="J50" s="40"/>
+      <c r="K50" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="L50" s="45"/>
-      <c r="M50" s="46" t="e">
+      <c r="L50" s="40"/>
+      <c r="M50" s="60" t="e">
         <f t="shared" ref="M50:M55" si="2">((I50-K50)/(E50-G50)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N50" s="46"/>
-      <c r="O50" s="35"/>
+      <c r="N50" s="60"/>
+      <c r="O50" s="39"/>
       <c r="P50" s="15"/>
     </row>
     <row r="51" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A51" s="35"/>
-      <c r="B51" s="35" t="s">
+      <c r="A51" s="39"/>
+      <c r="B51" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="35"/>
+      <c r="C51" s="39"/>
       <c r="D51" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E51" s="45" t="s">
+      <c r="E51" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45" t="s">
+      <c r="H51" s="40"/>
+      <c r="I51" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45" t="s">
+      <c r="J51" s="40"/>
+      <c r="K51" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="L51" s="45"/>
-      <c r="M51" s="46" t="e">
+      <c r="L51" s="40"/>
+      <c r="M51" s="60" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N51" s="46"/>
-      <c r="O51" s="35"/>
+      <c r="N51" s="60"/>
+      <c r="O51" s="39"/>
       <c r="P51" s="15"/>
     </row>
     <row r="52" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="35"/>
-      <c r="B52" s="35" t="s">
+      <c r="A52" s="39"/>
+      <c r="B52" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="35"/>
+      <c r="C52" s="39"/>
       <c r="D52" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="45" t="s">
+      <c r="E52" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="F52" s="45"/>
-      <c r="G52" s="45" t="s">
+      <c r="H52" s="40"/>
+      <c r="I52" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45" t="s">
+      <c r="J52" s="40"/>
+      <c r="K52" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="J52" s="45"/>
-      <c r="K52" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="L52" s="45"/>
-      <c r="M52" s="46" t="e">
+      <c r="L52" s="40"/>
+      <c r="M52" s="60" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N52" s="46"/>
-      <c r="O52" s="35"/>
+      <c r="N52" s="60"/>
+      <c r="O52" s="39"/>
       <c r="P52" s="15"/>
     </row>
     <row r="53" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="35"/>
-      <c r="B53" s="35" t="s">
+      <c r="A53" s="39"/>
+      <c r="B53" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="35"/>
+      <c r="C53" s="39"/>
       <c r="D53" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E53" s="45" t="s">
+      <c r="E53" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45" t="s">
+      <c r="H53" s="40"/>
+      <c r="I53" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45" t="s">
+      <c r="J53" s="40"/>
+      <c r="K53" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45" t="s">
-        <v>156</v>
-      </c>
-      <c r="L53" s="45"/>
-      <c r="M53" s="46" t="e">
+      <c r="L53" s="40"/>
+      <c r="M53" s="60" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N53" s="46"/>
-      <c r="O53" s="35"/>
+      <c r="N53" s="60"/>
+      <c r="O53" s="39"/>
       <c r="P53" s="15"/>
     </row>
     <row r="54" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="35"/>
-      <c r="B54" s="35" t="s">
+      <c r="A54" s="39"/>
+      <c r="B54" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="35"/>
+      <c r="C54" s="39"/>
       <c r="D54" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E54" s="45" t="s">
+      <c r="E54" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="F54" s="45"/>
-      <c r="G54" s="45" t="s">
+      <c r="H54" s="40"/>
+      <c r="I54" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45" t="s">
+      <c r="J54" s="40"/>
+      <c r="K54" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="L54" s="45"/>
-      <c r="M54" s="46" t="e">
+      <c r="L54" s="40"/>
+      <c r="M54" s="60" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N54" s="46"/>
-      <c r="O54" s="35"/>
+      <c r="N54" s="60"/>
+      <c r="O54" s="39"/>
       <c r="P54" s="15"/>
     </row>
     <row r="55" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="35"/>
-      <c r="B55" s="35" t="s">
+      <c r="A55" s="39"/>
+      <c r="B55" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="35"/>
+      <c r="C55" s="39"/>
       <c r="D55" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E55" s="45" t="s">
+      <c r="E55" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45" t="s">
+      <c r="H55" s="40"/>
+      <c r="I55" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45" t="s">
+      <c r="J55" s="40"/>
+      <c r="K55" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="L55" s="45"/>
-      <c r="M55" s="46" t="e">
+      <c r="L55" s="40"/>
+      <c r="M55" s="60" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N55" s="46"/>
-      <c r="O55" s="35"/>
+      <c r="N55" s="60"/>
+      <c r="O55" s="39"/>
       <c r="P55" s="15"/>
     </row>
     <row r="56" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A56" s="35"/>
-      <c r="B56" s="35" t="s">
+      <c r="A56" s="39"/>
+      <c r="B56" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="35"/>
+      <c r="C56" s="39"/>
       <c r="D56" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E56" s="45" t="s">
+      <c r="E56" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45" t="s">
+      <c r="H56" s="40"/>
+      <c r="I56" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45" t="s">
+      <c r="J56" s="40"/>
+      <c r="K56" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="L56" s="45"/>
-      <c r="M56" s="46" t="e">
+      <c r="L56" s="40"/>
+      <c r="M56" s="60" t="e">
         <f>((I56-K56)/(E56-G56)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N56" s="46"/>
-      <c r="O56" s="35"/>
+      <c r="N56" s="60"/>
+      <c r="O56" s="39"/>
       <c r="P56" s="15"/>
     </row>
     <row r="57" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="35"/>
-      <c r="B57" s="35" t="s">
+      <c r="A57" s="39"/>
+      <c r="B57" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="35"/>
+      <c r="C57" s="39"/>
       <c r="D57" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E57" s="45" t="s">
+      <c r="E57" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45" t="s">
+      <c r="H57" s="40"/>
+      <c r="I57" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45" t="s">
+      <c r="J57" s="40"/>
+      <c r="K57" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="J57" s="45"/>
-      <c r="K57" s="45" t="s">
-        <v>172</v>
-      </c>
-      <c r="L57" s="45"/>
-      <c r="M57" s="46" t="e">
+      <c r="L57" s="40"/>
+      <c r="M57" s="60" t="e">
         <f>((I57-K57)/(E57-G57)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N57" s="46"/>
-      <c r="O57" s="35"/>
+      <c r="N57" s="60"/>
+      <c r="O57" s="39"/>
       <c r="P57" s="15"/>
     </row>
     <row r="58" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="35"/>
-      <c r="B58" s="35" t="s">
+      <c r="A58" s="39"/>
+      <c r="B58" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="35"/>
+      <c r="C58" s="39"/>
       <c r="D58" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E58" s="45" t="s">
+      <c r="E58" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45" t="s">
+      <c r="H58" s="40"/>
+      <c r="I58" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45" t="s">
+      <c r="J58" s="40"/>
+      <c r="K58" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45" t="s">
-        <v>176</v>
-      </c>
-      <c r="L58" s="45"/>
-      <c r="M58" s="46" t="e">
+      <c r="L58" s="40"/>
+      <c r="M58" s="60" t="e">
         <f>((I58-K58)/(E58-G58)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N58" s="46"/>
-      <c r="O58" s="35"/>
+      <c r="N58" s="60"/>
+      <c r="O58" s="39"/>
       <c r="P58" s="15"/>
     </row>
     <row r="59" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A59" s="35"/>
-      <c r="B59" s="35" t="s">
+      <c r="A59" s="39"/>
+      <c r="B59" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="35"/>
+      <c r="C59" s="39"/>
       <c r="D59" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E59" s="45" t="s">
+      <c r="E59" s="40" t="s">
+        <v>643</v>
+      </c>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40" t="s">
         <v>644</v>
       </c>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45" t="s">
+      <c r="H59" s="40"/>
+      <c r="I59" s="40" t="s">
         <v>645</v>
       </c>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45" t="s">
+      <c r="J59" s="40"/>
+      <c r="K59" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45" t="s">
-        <v>647</v>
-      </c>
-      <c r="L59" s="45"/>
-      <c r="M59" s="46" t="e">
+      <c r="L59" s="40"/>
+      <c r="M59" s="60" t="e">
         <f t="shared" ref="M59:M64" si="3">((I59-K59)/(E59-G59)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N59" s="46"/>
-      <c r="O59" s="35"/>
+      <c r="N59" s="60"/>
+      <c r="O59" s="39"/>
       <c r="P59" s="15"/>
     </row>
     <row r="60" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A60" s="35"/>
-      <c r="B60" s="35" t="s">
+      <c r="A60" s="39"/>
+      <c r="B60" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="35"/>
+      <c r="C60" s="39"/>
       <c r="D60" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="40" t="s">
+        <v>647</v>
+      </c>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40" t="s">
         <v>648</v>
       </c>
-      <c r="F60" s="45"/>
-      <c r="G60" s="45" t="s">
+      <c r="H60" s="40"/>
+      <c r="I60" s="40" t="s">
         <v>649</v>
       </c>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45" t="s">
+      <c r="J60" s="40"/>
+      <c r="K60" s="40" t="s">
         <v>650</v>
       </c>
-      <c r="J60" s="45"/>
-      <c r="K60" s="45" t="s">
-        <v>651</v>
-      </c>
-      <c r="L60" s="45"/>
-      <c r="M60" s="46" t="e">
+      <c r="L60" s="40"/>
+      <c r="M60" s="60" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N60" s="46"/>
-      <c r="O60" s="35"/>
+      <c r="N60" s="60"/>
+      <c r="O60" s="39"/>
       <c r="P60" s="15"/>
     </row>
     <row r="61" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="35"/>
-      <c r="B61" s="35" t="s">
+      <c r="A61" s="39"/>
+      <c r="B61" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="35"/>
+      <c r="C61" s="39"/>
       <c r="D61" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E61" s="45" t="s">
+      <c r="E61" s="40" t="s">
+        <v>651</v>
+      </c>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40" t="s">
         <v>652</v>
       </c>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45" t="s">
+      <c r="H61" s="40"/>
+      <c r="I61" s="40" t="s">
         <v>653</v>
       </c>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45" t="s">
+      <c r="J61" s="40"/>
+      <c r="K61" s="40" t="s">
         <v>654</v>
       </c>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45" t="s">
-        <v>655</v>
-      </c>
-      <c r="L61" s="45"/>
-      <c r="M61" s="46" t="e">
+      <c r="L61" s="40"/>
+      <c r="M61" s="60" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N61" s="46"/>
-      <c r="O61" s="35"/>
+      <c r="N61" s="60"/>
+      <c r="O61" s="39"/>
       <c r="P61" s="15"/>
     </row>
     <row r="62" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A62" s="35"/>
-      <c r="B62" s="35" t="s">
+      <c r="A62" s="39"/>
+      <c r="B62" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="35"/>
+      <c r="C62" s="39"/>
       <c r="D62" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E62" s="45" t="s">
+      <c r="E62" s="40" t="s">
+        <v>655</v>
+      </c>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40" t="s">
         <v>656</v>
       </c>
-      <c r="F62" s="45"/>
-      <c r="G62" s="45" t="s">
+      <c r="H62" s="40"/>
+      <c r="I62" s="40" t="s">
         <v>657</v>
       </c>
-      <c r="H62" s="45"/>
-      <c r="I62" s="45" t="s">
+      <c r="J62" s="40"/>
+      <c r="K62" s="40" t="s">
         <v>658</v>
       </c>
-      <c r="J62" s="45"/>
-      <c r="K62" s="45" t="s">
-        <v>659</v>
-      </c>
-      <c r="L62" s="45"/>
-      <c r="M62" s="46" t="e">
+      <c r="L62" s="40"/>
+      <c r="M62" s="60" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N62" s="46"/>
-      <c r="O62" s="35"/>
+      <c r="N62" s="60"/>
+      <c r="O62" s="39"/>
       <c r="P62" s="15"/>
     </row>
     <row r="63" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A63" s="35"/>
-      <c r="B63" s="35" t="s">
+      <c r="A63" s="39"/>
+      <c r="B63" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C63" s="35"/>
+      <c r="C63" s="39"/>
       <c r="D63" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E63" s="45" t="s">
+      <c r="E63" s="40" t="s">
+        <v>659</v>
+      </c>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40" t="s">
         <v>660</v>
       </c>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45" t="s">
+      <c r="H63" s="40"/>
+      <c r="I63" s="40" t="s">
         <v>661</v>
       </c>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45" t="s">
+      <c r="J63" s="40"/>
+      <c r="K63" s="40" t="s">
         <v>662</v>
       </c>
-      <c r="J63" s="45"/>
-      <c r="K63" s="45" t="s">
-        <v>663</v>
-      </c>
-      <c r="L63" s="45"/>
-      <c r="M63" s="46" t="e">
+      <c r="L63" s="40"/>
+      <c r="M63" s="60" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N63" s="46"/>
-      <c r="O63" s="35"/>
+      <c r="N63" s="60"/>
+      <c r="O63" s="39"/>
       <c r="P63" s="15"/>
     </row>
     <row r="64" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A64" s="35"/>
-      <c r="B64" s="35" t="s">
+      <c r="A64" s="39"/>
+      <c r="B64" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="35"/>
+      <c r="C64" s="39"/>
       <c r="D64" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E64" s="45" t="s">
+      <c r="E64" s="40" t="s">
+        <v>663</v>
+      </c>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40" t="s">
         <v>664</v>
       </c>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45" t="s">
+      <c r="H64" s="40"/>
+      <c r="I64" s="40" t="s">
         <v>665</v>
       </c>
-      <c r="H64" s="45"/>
-      <c r="I64" s="45" t="s">
+      <c r="J64" s="40"/>
+      <c r="K64" s="40" t="s">
         <v>666</v>
       </c>
-      <c r="J64" s="45"/>
-      <c r="K64" s="45" t="s">
-        <v>667</v>
-      </c>
-      <c r="L64" s="45"/>
-      <c r="M64" s="46" t="e">
+      <c r="L64" s="40"/>
+      <c r="M64" s="60" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N64" s="46"/>
-      <c r="O64" s="35"/>
+      <c r="N64" s="60"/>
+      <c r="O64" s="39"/>
       <c r="P64" s="15"/>
     </row>
     <row r="65" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A65" s="35"/>
-      <c r="B65" s="35" t="s">
+      <c r="A65" s="39"/>
+      <c r="B65" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="35"/>
+      <c r="C65" s="39"/>
       <c r="D65" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E65" s="45" t="s">
+      <c r="E65" s="40" t="s">
+        <v>667</v>
+      </c>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40" t="s">
         <v>668</v>
       </c>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45" t="s">
+      <c r="H65" s="40"/>
+      <c r="I65" s="40" t="s">
         <v>669</v>
       </c>
-      <c r="H65" s="45"/>
-      <c r="I65" s="45" t="s">
+      <c r="J65" s="40"/>
+      <c r="K65" s="40" t="s">
         <v>670</v>
       </c>
-      <c r="J65" s="45"/>
-      <c r="K65" s="45" t="s">
-        <v>671</v>
-      </c>
-      <c r="L65" s="45"/>
-      <c r="M65" s="46" t="e">
+      <c r="L65" s="40"/>
+      <c r="M65" s="60" t="e">
         <f>((I65-K65)/(E65-G65)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N65" s="46"/>
-      <c r="O65" s="35"/>
+      <c r="N65" s="60"/>
+      <c r="O65" s="39"/>
       <c r="P65" s="15"/>
     </row>
     <row r="66" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A66" s="35">
+      <c r="A66" s="39">
         <v>3</v>
       </c>
-      <c r="B66" s="35" t="s">
+      <c r="B66" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C66" s="35"/>
+      <c r="C66" s="39"/>
       <c r="D66" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E66" s="45" t="s">
+      <c r="E66" s="40" t="s">
+        <v>671</v>
+      </c>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40" t="s">
         <v>672</v>
       </c>
-      <c r="F66" s="45"/>
-      <c r="G66" s="45" t="s">
+      <c r="H66" s="40"/>
+      <c r="I66" s="40" t="s">
         <v>673</v>
       </c>
-      <c r="H66" s="45"/>
-      <c r="I66" s="45" t="s">
+      <c r="J66" s="40"/>
+      <c r="K66" s="40" t="s">
         <v>674</v>
       </c>
-      <c r="J66" s="45"/>
-      <c r="K66" s="45" t="s">
-        <v>675</v>
-      </c>
-      <c r="L66" s="45"/>
-      <c r="M66" s="46" t="e">
+      <c r="L66" s="40"/>
+      <c r="M66" s="60" t="e">
         <f>((I66-K66)/(E66-G66)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N66" s="46"/>
-      <c r="O66" s="35"/>
+      <c r="N66" s="60"/>
+      <c r="O66" s="39"/>
       <c r="P66" s="15"/>
     </row>
     <row r="67" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A67" s="35"/>
-      <c r="B67" s="35" t="s">
+      <c r="A67" s="39"/>
+      <c r="B67" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="35"/>
+      <c r="C67" s="39"/>
       <c r="D67" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E67" s="45" t="s">
+      <c r="E67" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="F67" s="45"/>
-      <c r="G67" s="45" t="s">
+      <c r="H67" s="40"/>
+      <c r="I67" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="H67" s="45"/>
-      <c r="I67" s="45" t="s">
+      <c r="J67" s="40"/>
+      <c r="K67" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="J67" s="45"/>
-      <c r="K67" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="L67" s="45"/>
-      <c r="M67" s="46" t="e">
+      <c r="L67" s="40"/>
+      <c r="M67" s="60" t="e">
         <f t="shared" ref="M67:M72" si="4">((I67-K67)/(E67-G67)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N67" s="46"/>
-      <c r="O67" s="35"/>
+      <c r="N67" s="60"/>
+      <c r="O67" s="39"/>
       <c r="P67" s="15"/>
     </row>
     <row r="68" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A68" s="35"/>
-      <c r="B68" s="35" t="s">
+      <c r="A68" s="39"/>
+      <c r="B68" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C68" s="35"/>
+      <c r="C68" s="39"/>
       <c r="D68" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E68" s="45" t="s">
+      <c r="E68" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45" t="s">
+      <c r="H68" s="40"/>
+      <c r="I68" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="H68" s="45"/>
-      <c r="I68" s="45" t="s">
+      <c r="J68" s="40"/>
+      <c r="K68" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="J68" s="45"/>
-      <c r="K68" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="L68" s="45"/>
-      <c r="M68" s="46" t="e">
+      <c r="L68" s="40"/>
+      <c r="M68" s="60" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N68" s="46"/>
-      <c r="O68" s="35"/>
+      <c r="N68" s="60"/>
+      <c r="O68" s="39"/>
       <c r="P68" s="15"/>
     </row>
     <row r="69" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A69" s="35"/>
-      <c r="B69" s="35" t="s">
+      <c r="A69" s="39"/>
+      <c r="B69" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C69" s="35"/>
+      <c r="C69" s="39"/>
       <c r="D69" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E69" s="45" t="s">
+      <c r="E69" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="F69" s="45"/>
-      <c r="G69" s="45" t="s">
+      <c r="H69" s="40"/>
+      <c r="I69" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="H69" s="45"/>
-      <c r="I69" s="45" t="s">
+      <c r="J69" s="40"/>
+      <c r="K69" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="J69" s="45"/>
-      <c r="K69" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="L69" s="45"/>
-      <c r="M69" s="46" t="e">
+      <c r="L69" s="40"/>
+      <c r="M69" s="60" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N69" s="46"/>
-      <c r="O69" s="35"/>
+      <c r="N69" s="60"/>
+      <c r="O69" s="39"/>
       <c r="P69" s="15"/>
     </row>
     <row r="70" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A70" s="35"/>
-      <c r="B70" s="35" t="s">
+      <c r="A70" s="39"/>
+      <c r="B70" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C70" s="35"/>
+      <c r="C70" s="39"/>
       <c r="D70" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E70" s="45" t="s">
+      <c r="E70" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40" t="s">
         <v>189</v>
       </c>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45" t="s">
+      <c r="H70" s="40"/>
+      <c r="I70" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45" t="s">
+      <c r="J70" s="40"/>
+      <c r="K70" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="J70" s="45"/>
-      <c r="K70" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="L70" s="45"/>
-      <c r="M70" s="46" t="e">
+      <c r="L70" s="40"/>
+      <c r="M70" s="60" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N70" s="46"/>
-      <c r="O70" s="35"/>
+      <c r="N70" s="60"/>
+      <c r="O70" s="39"/>
       <c r="P70" s="15"/>
     </row>
     <row r="71" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A71" s="35"/>
-      <c r="B71" s="35" t="s">
+      <c r="A71" s="39"/>
+      <c r="B71" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C71" s="35"/>
+      <c r="C71" s="39"/>
       <c r="D71" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E71" s="45" t="s">
+      <c r="E71" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40" t="s">
         <v>193</v>
       </c>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45" t="s">
+      <c r="H71" s="40"/>
+      <c r="I71" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45" t="s">
+      <c r="J71" s="40"/>
+      <c r="K71" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="J71" s="45"/>
-      <c r="K71" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="L71" s="45"/>
-      <c r="M71" s="46" t="e">
+      <c r="L71" s="40"/>
+      <c r="M71" s="60" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N71" s="46"/>
-      <c r="O71" s="35"/>
+      <c r="N71" s="60"/>
+      <c r="O71" s="39"/>
       <c r="P71" s="15"/>
     </row>
     <row r="72" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A72" s="35"/>
-      <c r="B72" s="35" t="s">
+      <c r="A72" s="39"/>
+      <c r="B72" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C72" s="35"/>
+      <c r="C72" s="39"/>
       <c r="D72" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E72" s="45" t="s">
+      <c r="E72" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45" t="s">
+      <c r="H72" s="40"/>
+      <c r="I72" s="40" t="s">
         <v>198</v>
       </c>
-      <c r="H72" s="45"/>
-      <c r="I72" s="45" t="s">
+      <c r="J72" s="40"/>
+      <c r="K72" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="J72" s="45"/>
-      <c r="K72" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="L72" s="45"/>
-      <c r="M72" s="46" t="e">
+      <c r="L72" s="40"/>
+      <c r="M72" s="60" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N72" s="46"/>
-      <c r="O72" s="35"/>
+      <c r="N72" s="60"/>
+      <c r="O72" s="39"/>
       <c r="P72" s="15"/>
     </row>
     <row r="73" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="35"/>
-      <c r="B73" s="35" t="s">
+      <c r="A73" s="39"/>
+      <c r="B73" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C73" s="35"/>
+      <c r="C73" s="39"/>
       <c r="D73" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E73" s="45" t="s">
+      <c r="E73" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45" t="s">
+      <c r="H73" s="40"/>
+      <c r="I73" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="H73" s="45"/>
-      <c r="I73" s="45" t="s">
+      <c r="J73" s="40"/>
+      <c r="K73" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="J73" s="45"/>
-      <c r="K73" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="L73" s="45"/>
-      <c r="M73" s="46" t="e">
+      <c r="L73" s="40"/>
+      <c r="M73" s="60" t="e">
         <f>((I73-K73)/(E73-G73)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N73" s="46"/>
-      <c r="O73" s="35"/>
+      <c r="N73" s="60"/>
+      <c r="O73" s="39"/>
       <c r="P73" s="15"/>
     </row>
     <row r="74" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="47" t="s">
+      <c r="A74" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B74" s="38" t="s">
+      <c r="B74" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38" t="s">
+      <c r="C74" s="47"/>
+      <c r="D74" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E74" s="38" t="s">
+      <c r="E74" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38" t="s">
+      <c r="F74" s="47"/>
+      <c r="G74" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38" t="s">
+      <c r="H74" s="47"/>
+      <c r="I74" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="J74" s="38"/>
-      <c r="K74" s="38" t="s">
+      <c r="J74" s="47"/>
+      <c r="K74" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="L74" s="38"/>
-      <c r="M74" s="38" t="s">
+      <c r="L74" s="47"/>
+      <c r="M74" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="N74" s="38"/>
-      <c r="O74" s="38" t="s">
+      <c r="N74" s="47"/>
+      <c r="O74" s="47" t="s">
         <v>37</v>
       </c>
       <c r="P74" s="15"/>
     </row>
     <row r="75" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="38"/>
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
-      <c r="K75" s="38"/>
-      <c r="L75" s="38"/>
-      <c r="M75" s="38"/>
-      <c r="N75" s="38"/>
-      <c r="O75" s="38"/>
+      <c r="A75" s="45"/>
+      <c r="B75" s="47"/>
+      <c r="C75" s="47"/>
+      <c r="D75" s="47"/>
+      <c r="E75" s="47"/>
+      <c r="F75" s="47"/>
+      <c r="G75" s="47"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="47"/>
+      <c r="J75" s="47"/>
+      <c r="K75" s="47"/>
+      <c r="L75" s="47"/>
+      <c r="M75" s="47"/>
+      <c r="N75" s="47"/>
+      <c r="O75" s="47"/>
       <c r="P75" s="15"/>
     </row>
     <row r="76" spans="1:16" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="38"/>
-      <c r="N76" s="38"/>
-      <c r="O76" s="38"/>
+      <c r="A76" s="46"/>
+      <c r="B76" s="47"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="47"/>
+      <c r="F76" s="47"/>
+      <c r="G76" s="47"/>
+      <c r="H76" s="47"/>
+      <c r="I76" s="47"/>
+      <c r="J76" s="47"/>
+      <c r="K76" s="47"/>
+      <c r="L76" s="47"/>
+      <c r="M76" s="47"/>
+      <c r="N76" s="47"/>
+      <c r="O76" s="47"/>
       <c r="P76" s="15"/>
     </row>
     <row r="77" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A77" s="35">
+      <c r="A77" s="39">
         <v>3</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="B77" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C77" s="35"/>
+      <c r="C77" s="39"/>
       <c r="D77" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E77" s="45" t="s">
+      <c r="E77" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="F77" s="40"/>
+      <c r="G77" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="F77" s="45"/>
-      <c r="G77" s="45" t="s">
+      <c r="H77" s="40"/>
+      <c r="I77" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="H77" s="45"/>
-      <c r="I77" s="45" t="s">
+      <c r="J77" s="40"/>
+      <c r="K77" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="J77" s="45"/>
-      <c r="K77" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="L77" s="45"/>
-      <c r="M77" s="46" t="e">
+      <c r="L77" s="40"/>
+      <c r="M77" s="60" t="e">
         <f>((I77-K77)/(E77-G77)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N77" s="46"/>
-      <c r="O77" s="35" t="s">
+      <c r="N77" s="60"/>
+      <c r="O77" s="39" t="s">
         <v>38</v>
       </c>
       <c r="P77" s="15"/>
     </row>
     <row r="78" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A78" s="35"/>
-      <c r="B78" s="35" t="s">
+      <c r="A78" s="39"/>
+      <c r="B78" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="35"/>
+      <c r="C78" s="39"/>
       <c r="D78" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E78" s="45" t="s">
+      <c r="E78" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="F78" s="45"/>
-      <c r="G78" s="45" t="s">
+      <c r="H78" s="40"/>
+      <c r="I78" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="H78" s="45"/>
-      <c r="I78" s="45" t="s">
+      <c r="J78" s="40"/>
+      <c r="K78" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="J78" s="45"/>
-      <c r="K78" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="L78" s="45"/>
-      <c r="M78" s="46" t="e">
+      <c r="L78" s="40"/>
+      <c r="M78" s="60" t="e">
         <f>((I78-K78)/(E78-G78)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N78" s="46"/>
-      <c r="O78" s="35"/>
+      <c r="N78" s="60"/>
+      <c r="O78" s="39"/>
       <c r="P78" s="15"/>
     </row>
     <row r="79" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A79" s="35"/>
-      <c r="B79" s="35" t="s">
+      <c r="A79" s="39"/>
+      <c r="B79" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C79" s="35"/>
+      <c r="C79" s="39"/>
       <c r="D79" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E79" s="45" t="s">
+      <c r="E79" s="40" t="s">
+        <v>675</v>
+      </c>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40" t="s">
         <v>676</v>
       </c>
-      <c r="F79" s="45"/>
-      <c r="G79" s="45" t="s">
+      <c r="H79" s="40"/>
+      <c r="I79" s="40" t="s">
         <v>677</v>
       </c>
-      <c r="H79" s="45"/>
-      <c r="I79" s="45" t="s">
+      <c r="J79" s="40"/>
+      <c r="K79" s="40" t="s">
         <v>678</v>
       </c>
-      <c r="J79" s="45"/>
-      <c r="K79" s="45" t="s">
-        <v>679</v>
-      </c>
-      <c r="L79" s="45"/>
-      <c r="M79" s="46" t="e">
+      <c r="L79" s="40"/>
+      <c r="M79" s="60" t="e">
         <f t="shared" ref="M79:M84" si="5">((I79-K79)/(E79-G79)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N79" s="46"/>
-      <c r="O79" s="35"/>
+      <c r="N79" s="60"/>
+      <c r="O79" s="39"/>
       <c r="P79" s="15"/>
     </row>
     <row r="80" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A80" s="35"/>
-      <c r="B80" s="35" t="s">
+      <c r="A80" s="39"/>
+      <c r="B80" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="35"/>
+      <c r="C80" s="39"/>
       <c r="D80" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E80" s="45" t="s">
+      <c r="E80" s="40" t="s">
+        <v>679</v>
+      </c>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40" t="s">
         <v>680</v>
       </c>
-      <c r="F80" s="45"/>
-      <c r="G80" s="45" t="s">
+      <c r="H80" s="40"/>
+      <c r="I80" s="40" t="s">
         <v>681</v>
       </c>
-      <c r="H80" s="45"/>
-      <c r="I80" s="45" t="s">
+      <c r="J80" s="40"/>
+      <c r="K80" s="40" t="s">
         <v>682</v>
       </c>
-      <c r="J80" s="45"/>
-      <c r="K80" s="45" t="s">
-        <v>683</v>
-      </c>
-      <c r="L80" s="45"/>
-      <c r="M80" s="46" t="e">
+      <c r="L80" s="40"/>
+      <c r="M80" s="60" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N80" s="46"/>
-      <c r="O80" s="35"/>
+      <c r="N80" s="60"/>
+      <c r="O80" s="39"/>
       <c r="P80" s="15"/>
     </row>
     <row r="81" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A81" s="35"/>
-      <c r="B81" s="35" t="s">
+      <c r="A81" s="39"/>
+      <c r="B81" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C81" s="35"/>
+      <c r="C81" s="39"/>
       <c r="D81" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E81" s="45" t="s">
+      <c r="E81" s="40" t="s">
+        <v>683</v>
+      </c>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40" t="s">
         <v>684</v>
       </c>
-      <c r="F81" s="45"/>
-      <c r="G81" s="45" t="s">
+      <c r="H81" s="40"/>
+      <c r="I81" s="40" t="s">
         <v>685</v>
       </c>
-      <c r="H81" s="45"/>
-      <c r="I81" s="45" t="s">
+      <c r="J81" s="40"/>
+      <c r="K81" s="40" t="s">
         <v>686</v>
       </c>
-      <c r="J81" s="45"/>
-      <c r="K81" s="45" t="s">
-        <v>687</v>
-      </c>
-      <c r="L81" s="45"/>
-      <c r="M81" s="46" t="e">
+      <c r="L81" s="40"/>
+      <c r="M81" s="60" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N81" s="46"/>
-      <c r="O81" s="35"/>
+      <c r="N81" s="60"/>
+      <c r="O81" s="39"/>
       <c r="P81" s="15"/>
     </row>
     <row r="82" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="35"/>
-      <c r="B82" s="35" t="s">
+      <c r="A82" s="39"/>
+      <c r="B82" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="35"/>
+      <c r="C82" s="39"/>
       <c r="D82" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E82" s="45" t="s">
+      <c r="E82" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40" t="s">
         <v>688</v>
       </c>
-      <c r="F82" s="45"/>
-      <c r="G82" s="45" t="s">
+      <c r="H82" s="40"/>
+      <c r="I82" s="40" t="s">
         <v>689</v>
       </c>
-      <c r="H82" s="45"/>
-      <c r="I82" s="45" t="s">
+      <c r="J82" s="40"/>
+      <c r="K82" s="40" t="s">
         <v>690</v>
       </c>
-      <c r="J82" s="45"/>
-      <c r="K82" s="45" t="s">
-        <v>691</v>
-      </c>
-      <c r="L82" s="45"/>
-      <c r="M82" s="46" t="e">
+      <c r="L82" s="40"/>
+      <c r="M82" s="60" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N82" s="46"/>
-      <c r="O82" s="35"/>
+      <c r="N82" s="60"/>
+      <c r="O82" s="39"/>
       <c r="P82" s="15"/>
     </row>
     <row r="83" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A83" s="35"/>
-      <c r="B83" s="35" t="s">
+      <c r="A83" s="39"/>
+      <c r="B83" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C83" s="35"/>
+      <c r="C83" s="39"/>
       <c r="D83" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E83" s="45" t="s">
+      <c r="E83" s="40" t="s">
+        <v>691</v>
+      </c>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40" t="s">
         <v>692</v>
       </c>
-      <c r="F83" s="45"/>
-      <c r="G83" s="45" t="s">
+      <c r="H83" s="40"/>
+      <c r="I83" s="40" t="s">
         <v>693</v>
       </c>
-      <c r="H83" s="45"/>
-      <c r="I83" s="45" t="s">
+      <c r="J83" s="40"/>
+      <c r="K83" s="40" t="s">
         <v>694</v>
       </c>
-      <c r="J83" s="45"/>
-      <c r="K83" s="45" t="s">
-        <v>695</v>
-      </c>
-      <c r="L83" s="45"/>
-      <c r="M83" s="46" t="e">
+      <c r="L83" s="40"/>
+      <c r="M83" s="60" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N83" s="46"/>
-      <c r="O83" s="35"/>
+      <c r="N83" s="60"/>
+      <c r="O83" s="39"/>
       <c r="P83" s="15"/>
     </row>
     <row r="84" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A84" s="35"/>
-      <c r="B84" s="35" t="s">
+      <c r="A84" s="39"/>
+      <c r="B84" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="35"/>
+      <c r="C84" s="39"/>
       <c r="D84" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E84" s="45" t="s">
+      <c r="E84" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40" t="s">
         <v>696</v>
       </c>
-      <c r="F84" s="45"/>
-      <c r="G84" s="45" t="s">
+      <c r="H84" s="40"/>
+      <c r="I84" s="40" t="s">
         <v>697</v>
       </c>
-      <c r="H84" s="45"/>
-      <c r="I84" s="45" t="s">
+      <c r="J84" s="40"/>
+      <c r="K84" s="40" t="s">
         <v>698</v>
       </c>
-      <c r="J84" s="45"/>
-      <c r="K84" s="45" t="s">
-        <v>699</v>
-      </c>
-      <c r="L84" s="45"/>
-      <c r="M84" s="46" t="e">
+      <c r="L84" s="40"/>
+      <c r="M84" s="60" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N84" s="46"/>
-      <c r="O84" s="35"/>
+      <c r="N84" s="60"/>
+      <c r="O84" s="39"/>
       <c r="P84" s="15"/>
     </row>
     <row r="85" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A85" s="35"/>
-      <c r="B85" s="35" t="s">
+      <c r="A85" s="39"/>
+      <c r="B85" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C85" s="35"/>
+      <c r="C85" s="39"/>
       <c r="D85" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E85" s="45" t="s">
+      <c r="E85" s="40" t="s">
+        <v>699</v>
+      </c>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40" t="s">
         <v>700</v>
       </c>
-      <c r="F85" s="45"/>
-      <c r="G85" s="45" t="s">
+      <c r="H85" s="40"/>
+      <c r="I85" s="40" t="s">
         <v>701</v>
       </c>
-      <c r="H85" s="45"/>
-      <c r="I85" s="45" t="s">
+      <c r="J85" s="40"/>
+      <c r="K85" s="40" t="s">
         <v>702</v>
       </c>
-      <c r="J85" s="45"/>
-      <c r="K85" s="45" t="s">
-        <v>703</v>
-      </c>
-      <c r="L85" s="45"/>
-      <c r="M85" s="46" t="e">
+      <c r="L85" s="40"/>
+      <c r="M85" s="60" t="e">
         <f>((I85-K85)/(E85-G85)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N85" s="46"/>
-      <c r="O85" s="35"/>
+      <c r="N85" s="60"/>
+      <c r="O85" s="39"/>
       <c r="P85" s="15"/>
     </row>
     <row r="86" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A86" s="35">
+      <c r="A86" s="39">
         <v>4</v>
       </c>
-      <c r="B86" s="35" t="s">
+      <c r="B86" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C86" s="35"/>
+      <c r="C86" s="39"/>
       <c r="D86" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E86" s="45" t="s">
+      <c r="E86" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="F86" s="45"/>
-      <c r="G86" s="45" t="s">
+      <c r="H86" s="40"/>
+      <c r="I86" s="40" t="s">
         <v>705</v>
       </c>
-      <c r="H86" s="45"/>
-      <c r="I86" s="45" t="s">
+      <c r="J86" s="40"/>
+      <c r="K86" s="40" t="s">
         <v>706</v>
       </c>
-      <c r="J86" s="45"/>
-      <c r="K86" s="45" t="s">
-        <v>707</v>
-      </c>
-      <c r="L86" s="45"/>
-      <c r="M86" s="46" t="e">
+      <c r="L86" s="40"/>
+      <c r="M86" s="60" t="e">
         <f>((I86-K86)/(E86-G86)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N86" s="46"/>
-      <c r="O86" s="35"/>
+      <c r="N86" s="60"/>
+      <c r="O86" s="39"/>
       <c r="P86" s="15"/>
     </row>
     <row r="87" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35" t="s">
+      <c r="A87" s="39"/>
+      <c r="B87" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C87" s="35"/>
+      <c r="C87" s="39"/>
       <c r="D87" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E87" s="45" t="s">
+      <c r="E87" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="F87" s="45"/>
-      <c r="G87" s="45" t="s">
+      <c r="H87" s="40"/>
+      <c r="I87" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="H87" s="45"/>
-      <c r="I87" s="45" t="s">
+      <c r="J87" s="40"/>
+      <c r="K87" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="J87" s="45"/>
-      <c r="K87" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="L87" s="45"/>
-      <c r="M87" s="46" t="e">
+      <c r="L87" s="40"/>
+      <c r="M87" s="60" t="e">
         <f t="shared" ref="M87:M92" si="6">((I87-K87)/(E87-G87)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N87" s="46"/>
-      <c r="O87" s="35"/>
+      <c r="N87" s="60"/>
+      <c r="O87" s="39"/>
       <c r="P87" s="15"/>
     </row>
     <row r="88" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35" t="s">
+      <c r="A88" s="39"/>
+      <c r="B88" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C88" s="35"/>
+      <c r="C88" s="39"/>
       <c r="D88" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E88" s="45" t="s">
+      <c r="E88" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="F88" s="45"/>
-      <c r="G88" s="45" t="s">
+      <c r="H88" s="40"/>
+      <c r="I88" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="H88" s="45"/>
-      <c r="I88" s="45" t="s">
+      <c r="J88" s="40"/>
+      <c r="K88" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="J88" s="45"/>
-      <c r="K88" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="L88" s="45"/>
-      <c r="M88" s="46" t="e">
+      <c r="L88" s="40"/>
+      <c r="M88" s="60" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N88" s="46"/>
-      <c r="O88" s="35"/>
+      <c r="N88" s="60"/>
+      <c r="O88" s="39"/>
       <c r="P88" s="15"/>
     </row>
     <row r="89" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A89" s="35"/>
-      <c r="B89" s="35" t="s">
+      <c r="A89" s="39"/>
+      <c r="B89" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C89" s="35"/>
+      <c r="C89" s="39"/>
       <c r="D89" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E89" s="45" t="s">
+      <c r="E89" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="F89" s="40"/>
+      <c r="G89" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="F89" s="45"/>
-      <c r="G89" s="45" t="s">
+      <c r="H89" s="40"/>
+      <c r="I89" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="H89" s="45"/>
-      <c r="I89" s="45" t="s">
+      <c r="J89" s="40"/>
+      <c r="K89" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="J89" s="45"/>
-      <c r="K89" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="L89" s="45"/>
-      <c r="M89" s="46" t="e">
+      <c r="L89" s="40"/>
+      <c r="M89" s="60" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N89" s="46"/>
-      <c r="O89" s="35"/>
+      <c r="N89" s="60"/>
+      <c r="O89" s="39"/>
       <c r="P89" s="15"/>
     </row>
     <row r="90" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A90" s="35"/>
-      <c r="B90" s="35" t="s">
+      <c r="A90" s="39"/>
+      <c r="B90" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="35"/>
+      <c r="C90" s="39"/>
       <c r="D90" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E90" s="45" t="s">
+      <c r="E90" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="F90" s="40"/>
+      <c r="G90" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="F90" s="45"/>
-      <c r="G90" s="45" t="s">
+      <c r="H90" s="40"/>
+      <c r="I90" s="40" t="s">
         <v>226</v>
       </c>
-      <c r="H90" s="45"/>
-      <c r="I90" s="45" t="s">
+      <c r="J90" s="40"/>
+      <c r="K90" s="40" t="s">
         <v>227</v>
       </c>
-      <c r="J90" s="45"/>
-      <c r="K90" s="45" t="s">
-        <v>228</v>
-      </c>
-      <c r="L90" s="45"/>
-      <c r="M90" s="46" t="e">
+      <c r="L90" s="40"/>
+      <c r="M90" s="60" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N90" s="46"/>
-      <c r="O90" s="35"/>
+      <c r="N90" s="60"/>
+      <c r="O90" s="39"/>
       <c r="P90" s="15"/>
     </row>
     <row r="91" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A91" s="35"/>
-      <c r="B91" s="35" t="s">
+      <c r="A91" s="39"/>
+      <c r="B91" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C91" s="35"/>
+      <c r="C91" s="39"/>
       <c r="D91" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E91" s="45" t="s">
+      <c r="E91" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="F91" s="40"/>
+      <c r="G91" s="40" t="s">
         <v>229</v>
       </c>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45" t="s">
+      <c r="H91" s="40"/>
+      <c r="I91" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45" t="s">
+      <c r="J91" s="40"/>
+      <c r="K91" s="40" t="s">
         <v>231</v>
       </c>
-      <c r="J91" s="45"/>
-      <c r="K91" s="45" t="s">
-        <v>232</v>
-      </c>
-      <c r="L91" s="45"/>
-      <c r="M91" s="46" t="e">
+      <c r="L91" s="40"/>
+      <c r="M91" s="60" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N91" s="46"/>
-      <c r="O91" s="35"/>
+      <c r="N91" s="60"/>
+      <c r="O91" s="39"/>
       <c r="P91" s="15"/>
     </row>
     <row r="92" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A92" s="35"/>
-      <c r="B92" s="35" t="s">
+      <c r="A92" s="39"/>
+      <c r="B92" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C92" s="35"/>
+      <c r="C92" s="39"/>
       <c r="D92" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E92" s="45" t="s">
+      <c r="E92" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="F92" s="40"/>
+      <c r="G92" s="40" t="s">
         <v>233</v>
       </c>
-      <c r="F92" s="45"/>
-      <c r="G92" s="45" t="s">
+      <c r="H92" s="40"/>
+      <c r="I92" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="H92" s="45"/>
-      <c r="I92" s="45" t="s">
+      <c r="J92" s="40"/>
+      <c r="K92" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="J92" s="45"/>
-      <c r="K92" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="L92" s="45"/>
-      <c r="M92" s="46" t="e">
+      <c r="L92" s="40"/>
+      <c r="M92" s="60" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N92" s="46"/>
-      <c r="O92" s="35"/>
+      <c r="N92" s="60"/>
+      <c r="O92" s="39"/>
       <c r="P92" s="15"/>
     </row>
     <row r="93" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A93" s="35"/>
-      <c r="B93" s="35" t="s">
+      <c r="A93" s="39"/>
+      <c r="B93" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C93" s="35"/>
+      <c r="C93" s="39"/>
       <c r="D93" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E93" s="45" t="s">
+      <c r="E93" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="F93" s="40"/>
+      <c r="G93" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="F93" s="45"/>
-      <c r="G93" s="45" t="s">
+      <c r="H93" s="40"/>
+      <c r="I93" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="H93" s="45"/>
-      <c r="I93" s="45" t="s">
+      <c r="J93" s="40"/>
+      <c r="K93" s="40" t="s">
         <v>239</v>
       </c>
-      <c r="J93" s="45"/>
-      <c r="K93" s="45" t="s">
-        <v>240</v>
-      </c>
-      <c r="L93" s="45"/>
-      <c r="M93" s="46" t="e">
+      <c r="L93" s="40"/>
+      <c r="M93" s="60" t="e">
         <f>((I93-K93)/(E93-G93)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N93" s="46"/>
-      <c r="O93" s="35"/>
+      <c r="N93" s="60"/>
+      <c r="O93" s="39"/>
       <c r="P93" s="15"/>
     </row>
     <row r="94" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A94" s="35"/>
-      <c r="B94" s="35" t="s">
+      <c r="A94" s="39"/>
+      <c r="B94" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C94" s="35"/>
+      <c r="C94" s="39"/>
       <c r="D94" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E94" s="45" t="s">
+      <c r="E94" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="F94" s="40"/>
+      <c r="G94" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="F94" s="45"/>
-      <c r="G94" s="45" t="s">
+      <c r="H94" s="40"/>
+      <c r="I94" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="H94" s="45"/>
-      <c r="I94" s="45" t="s">
+      <c r="J94" s="40"/>
+      <c r="K94" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="J94" s="45"/>
-      <c r="K94" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="L94" s="45"/>
-      <c r="M94" s="46" t="e">
+      <c r="L94" s="40"/>
+      <c r="M94" s="60" t="e">
         <f>((I94-K94)/(E94-G94)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N94" s="46"/>
-      <c r="O94" s="35"/>
+      <c r="N94" s="60"/>
+      <c r="O94" s="39"/>
       <c r="P94" s="15"/>
     </row>
     <row r="95" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A95" s="35"/>
-      <c r="B95" s="35" t="s">
+      <c r="A95" s="39"/>
+      <c r="B95" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C95" s="35"/>
+      <c r="C95" s="39"/>
       <c r="D95" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E95" s="45" t="s">
+      <c r="E95" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="F95" s="40"/>
+      <c r="G95" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="F95" s="45"/>
-      <c r="G95" s="45" t="s">
+      <c r="H95" s="40"/>
+      <c r="I95" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="H95" s="45"/>
-      <c r="I95" s="45" t="s">
+      <c r="J95" s="40"/>
+      <c r="K95" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="J95" s="45"/>
-      <c r="K95" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="L95" s="45"/>
-      <c r="M95" s="46" t="e">
+      <c r="L95" s="40"/>
+      <c r="M95" s="60" t="e">
         <f>((I95-K95)/(E95-G95)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N95" s="46"/>
-      <c r="O95" s="35"/>
+      <c r="N95" s="60"/>
+      <c r="O95" s="39"/>
       <c r="P95" s="15"/>
     </row>
     <row r="96" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A96" s="35"/>
-      <c r="B96" s="35" t="s">
+      <c r="A96" s="39"/>
+      <c r="B96" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C96" s="35"/>
+      <c r="C96" s="39"/>
       <c r="D96" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E96" s="45" t="s">
+      <c r="E96" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="F96" s="40"/>
+      <c r="G96" s="40" t="s">
         <v>708</v>
       </c>
-      <c r="F96" s="45"/>
-      <c r="G96" s="45" t="s">
+      <c r="H96" s="40"/>
+      <c r="I96" s="40" t="s">
         <v>709</v>
       </c>
-      <c r="H96" s="45"/>
-      <c r="I96" s="45" t="s">
+      <c r="J96" s="40"/>
+      <c r="K96" s="40" t="s">
         <v>710</v>
       </c>
-      <c r="J96" s="45"/>
-      <c r="K96" s="45" t="s">
-        <v>711</v>
-      </c>
-      <c r="L96" s="45"/>
-      <c r="M96" s="46" t="e">
+      <c r="L96" s="40"/>
+      <c r="M96" s="60" t="e">
         <f t="shared" ref="M96:M101" si="7">((I96-K96)/(E96-G96)-1)*75</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N96" s="46"/>
-      <c r="O96" s="35"/>
+      <c r="N96" s="60"/>
+      <c r="O96" s="39"/>
       <c r="P96" s="15"/>
     </row>
     <row r="97" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A97" s="35"/>
-      <c r="B97" s="35" t="s">
+      <c r="A97" s="39"/>
+      <c r="B97" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C97" s="35"/>
+      <c r="C97" s="39"/>
       <c r="D97" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E97" s="45" t="s">
+      <c r="E97" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="F97" s="40"/>
+      <c r="G97" s="40" t="s">
         <v>712</v>
       </c>
-      <c r="F97" s="45"/>
-      <c r="G97" s="45" t="s">
+      <c r="H97" s="40"/>
+      <c r="I97" s="40" t="s">
         <v>713</v>
       </c>
-      <c r="H97" s="45"/>
-      <c r="I97" s="45" t="s">
+      <c r="J97" s="40"/>
+      <c r="K97" s="40" t="s">
         <v>714</v>
       </c>
-      <c r="J97" s="45"/>
-      <c r="K97" s="45" t="s">
-        <v>715</v>
-      </c>
-      <c r="L97" s="45"/>
-      <c r="M97" s="46" t="e">
+      <c r="L97" s="40"/>
+      <c r="M97" s="60" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N97" s="46"/>
-      <c r="O97" s="35"/>
+      <c r="N97" s="60"/>
+      <c r="O97" s="39"/>
       <c r="P97" s="15"/>
     </row>
     <row r="98" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A98" s="35"/>
-      <c r="B98" s="35" t="s">
+      <c r="A98" s="39"/>
+      <c r="B98" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="35"/>
+      <c r="C98" s="39"/>
       <c r="D98" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E98" s="45" t="s">
+      <c r="E98" s="40" t="s">
+        <v>715</v>
+      </c>
+      <c r="F98" s="40"/>
+      <c r="G98" s="40" t="s">
         <v>716</v>
       </c>
-      <c r="F98" s="45"/>
-      <c r="G98" s="45" t="s">
+      <c r="H98" s="40"/>
+      <c r="I98" s="40" t="s">
         <v>717</v>
       </c>
-      <c r="H98" s="45"/>
-      <c r="I98" s="45" t="s">
+      <c r="J98" s="40"/>
+      <c r="K98" s="40" t="s">
         <v>718</v>
       </c>
-      <c r="J98" s="45"/>
-      <c r="K98" s="45" t="s">
-        <v>719</v>
-      </c>
-      <c r="L98" s="45"/>
-      <c r="M98" s="46" t="e">
+      <c r="L98" s="40"/>
+      <c r="M98" s="60" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N98" s="46"/>
-      <c r="O98" s="35"/>
+      <c r="N98" s="60"/>
+      <c r="O98" s="39"/>
       <c r="P98" s="15"/>
     </row>
     <row r="99" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A99" s="35"/>
-      <c r="B99" s="35" t="s">
+      <c r="A99" s="39"/>
+      <c r="B99" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C99" s="35"/>
+      <c r="C99" s="39"/>
       <c r="D99" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="45" t="s">
+      <c r="E99" s="40" t="s">
+        <v>719</v>
+      </c>
+      <c r="F99" s="40"/>
+      <c r="G99" s="40" t="s">
         <v>720</v>
       </c>
-      <c r="F99" s="45"/>
-      <c r="G99" s="45" t="s">
+      <c r="H99" s="40"/>
+      <c r="I99" s="40" t="s">
         <v>721</v>
       </c>
-      <c r="H99" s="45"/>
-      <c r="I99" s="45" t="s">
+      <c r="J99" s="40"/>
+      <c r="K99" s="40" t="s">
         <v>722</v>
       </c>
-      <c r="J99" s="45"/>
-      <c r="K99" s="45" t="s">
-        <v>723</v>
-      </c>
-      <c r="L99" s="45"/>
-      <c r="M99" s="46" t="e">
+      <c r="L99" s="40"/>
+      <c r="M99" s="60" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N99" s="46"/>
-      <c r="O99" s="35"/>
+      <c r="N99" s="60"/>
+      <c r="O99" s="39"/>
       <c r="P99" s="15"/>
     </row>
     <row r="100" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A100" s="35"/>
-      <c r="B100" s="35" t="s">
+      <c r="A100" s="39"/>
+      <c r="B100" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C100" s="35"/>
+      <c r="C100" s="39"/>
       <c r="D100" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E100" s="45" t="s">
+      <c r="E100" s="40" t="s">
+        <v>723</v>
+      </c>
+      <c r="F100" s="40"/>
+      <c r="G100" s="40" t="s">
         <v>724</v>
       </c>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45" t="s">
+      <c r="H100" s="40"/>
+      <c r="I100" s="40" t="s">
         <v>725</v>
       </c>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45" t="s">
+      <c r="J100" s="40"/>
+      <c r="K100" s="40" t="s">
         <v>726</v>
       </c>
-      <c r="J100" s="45"/>
-      <c r="K100" s="45" t="s">
-        <v>727</v>
-      </c>
-      <c r="L100" s="45"/>
-      <c r="M100" s="46" t="e">
+      <c r="L100" s="40"/>
+      <c r="M100" s="60" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N100" s="46"/>
-      <c r="O100" s="35"/>
+      <c r="N100" s="60"/>
+      <c r="O100" s="39"/>
       <c r="P100" s="15"/>
     </row>
     <row r="101" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A101" s="35"/>
-      <c r="B101" s="35" t="s">
+      <c r="A101" s="39"/>
+      <c r="B101" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="35"/>
+      <c r="C101" s="39"/>
       <c r="D101" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E101" s="45" t="s">
+      <c r="E101" s="40" t="s">
+        <v>727</v>
+      </c>
+      <c r="F101" s="40"/>
+      <c r="G101" s="40" t="s">
         <v>728</v>
       </c>
-      <c r="F101" s="45"/>
-      <c r="G101" s="45" t="s">
+      <c r="H101" s="40"/>
+      <c r="I101" s="40" t="s">
         <v>729</v>
       </c>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45" t="s">
+      <c r="J101" s="40"/>
+      <c r="K101" s="40" t="s">
         <v>730</v>
       </c>
-      <c r="J101" s="45"/>
-      <c r="K101" s="45" t="s">
-        <v>731</v>
-      </c>
-      <c r="L101" s="45"/>
-      <c r="M101" s="46" t="e">
+      <c r="L101" s="40"/>
+      <c r="M101" s="60" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N101" s="46"/>
-      <c r="O101" s="35"/>
+      <c r="N101" s="60"/>
+      <c r="O101" s="39"/>
       <c r="P101" s="15"/>
     </row>
     <row r="102" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A102" s="35"/>
-      <c r="B102" s="35" t="s">
+      <c r="A102" s="39"/>
+      <c r="B102" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C102" s="35"/>
+      <c r="C102" s="39"/>
       <c r="D102" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E102" s="45" t="s">
+      <c r="E102" s="40" t="s">
+        <v>731</v>
+      </c>
+      <c r="F102" s="40"/>
+      <c r="G102" s="40" t="s">
         <v>732</v>
       </c>
-      <c r="F102" s="45"/>
-      <c r="G102" s="45" t="s">
+      <c r="H102" s="40"/>
+      <c r="I102" s="40" t="s">
         <v>733</v>
       </c>
-      <c r="H102" s="45"/>
-      <c r="I102" s="45" t="s">
+      <c r="J102" s="40"/>
+      <c r="K102" s="40" t="s">
         <v>734</v>
       </c>
-      <c r="J102" s="45"/>
-      <c r="K102" s="45" t="s">
-        <v>735</v>
-      </c>
-      <c r="L102" s="45"/>
-      <c r="M102" s="46" t="e">
+      <c r="L102" s="40"/>
+      <c r="M102" s="60" t="e">
         <f>((I102-K102)/(E102-G102)-1)*60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N102" s="46"/>
-      <c r="O102" s="35"/>
+      <c r="N102" s="60"/>
+      <c r="O102" s="39"/>
       <c r="P102" s="15"/>
     </row>
     <row r="103" spans="1:16" s="1" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7187,10 +7178,10 @@
         <v>42</v>
       </c>
       <c r="C106" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="D106" s="16" t="s">
         <v>736</v>
-      </c>
-      <c r="D106" s="16" t="s">
-        <v>737</v>
       </c>
       <c r="E106" s="16" t="s">
         <v>81</v>
@@ -7199,7 +7190,7 @@
         <v>82</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H106" s="21" t="s">
         <v>45</v>
@@ -7214,29 +7205,29 @@
       <c r="P106" s="15"/>
     </row>
     <row r="107" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A107" s="42">
+      <c r="A107" s="41">
         <v>1</v>
       </c>
       <c r="B107" s="22">
         <v>5</v>
       </c>
       <c r="C107" s="30" t="s">
+        <v>556</v>
+      </c>
+      <c r="D107" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="D107" s="30" t="s">
+      <c r="E107" s="30" t="s">
         <v>558</v>
       </c>
-      <c r="E107" s="30" t="s">
+      <c r="F107" s="30" t="s">
         <v>559</v>
-      </c>
-      <c r="F107" s="30" t="s">
-        <v>560</v>
       </c>
       <c r="G107" s="26" t="e">
         <f>20*LOG10((E107/F107)/(C107/D107))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H107" s="42" t="s">
+      <c r="H107" s="41" t="s">
         <v>46</v>
       </c>
       <c r="I107" s="15"/>
@@ -7249,27 +7240,27 @@
       <c r="P107" s="15"/>
     </row>
     <row r="108" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A108" s="43"/>
+      <c r="A108" s="42"/>
       <c r="B108" s="22">
         <v>10</v>
       </c>
       <c r="C108" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D108" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="D108" s="30" t="s">
+      <c r="E108" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="E108" s="30" t="s">
+      <c r="F108" s="30" t="s">
         <v>251</v>
-      </c>
-      <c r="F108" s="30" t="s">
-        <v>252</v>
       </c>
       <c r="G108" s="26" t="e">
         <f t="shared" ref="G108:G115" si="8">20*LOG10((E108/F108)/(C108/D108))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H108" s="43"/>
+      <c r="H108" s="42"/>
       <c r="I108" s="15"/>
       <c r="J108" s="15"/>
       <c r="K108" s="27"/>
@@ -7280,27 +7271,27 @@
       <c r="P108" s="15"/>
     </row>
     <row r="109" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A109" s="44"/>
+      <c r="A109" s="43"/>
       <c r="B109" s="23">
         <v>20</v>
       </c>
       <c r="C109" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="D109" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="D109" s="30" t="s">
+      <c r="E109" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="E109" s="30" t="s">
+      <c r="F109" s="30" t="s">
         <v>255</v>
-      </c>
-      <c r="F109" s="30" t="s">
-        <v>256</v>
       </c>
       <c r="G109" s="26" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H109" s="44"/>
+      <c r="H109" s="43"/>
       <c r="I109" s="15"/>
       <c r="J109" s="15"/>
       <c r="K109" s="15"/>
@@ -7318,10 +7309,10 @@
         <v>42</v>
       </c>
       <c r="C110" s="16" t="s">
+        <v>738</v>
+      </c>
+      <c r="D110" s="16" t="s">
         <v>739</v>
-      </c>
-      <c r="D110" s="16" t="s">
-        <v>740</v>
       </c>
       <c r="E110" s="16" t="s">
         <v>43</v>
@@ -7330,7 +7321,7 @@
         <v>44</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>45</v>
@@ -7345,29 +7336,29 @@
       <c r="P110" s="15"/>
     </row>
     <row r="111" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A111" s="42">
+      <c r="A111" s="41">
         <v>1</v>
       </c>
       <c r="B111" s="23">
         <v>50</v>
       </c>
       <c r="C111" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D111" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="D111" s="30" t="s">
+      <c r="E111" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="E111" s="30" t="s">
+      <c r="F111" s="30" t="s">
         <v>259</v>
-      </c>
-      <c r="F111" s="30" t="s">
-        <v>260</v>
       </c>
       <c r="G111" s="26" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H111" s="42" t="s">
+      <c r="H111" s="41" t="s">
         <v>46</v>
       </c>
       <c r="I111" s="15"/>
@@ -7380,27 +7371,27 @@
       <c r="P111" s="15"/>
     </row>
     <row r="112" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A112" s="43"/>
+      <c r="A112" s="42"/>
       <c r="B112" s="23">
         <v>100</v>
       </c>
       <c r="C112" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="D112" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="D112" s="30" t="s">
+      <c r="E112" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="E112" s="30" t="s">
+      <c r="F112" s="30" t="s">
         <v>263</v>
-      </c>
-      <c r="F112" s="30" t="s">
-        <v>264</v>
       </c>
       <c r="G112" s="26" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H112" s="43"/>
+      <c r="H112" s="42"/>
       <c r="I112" s="15"/>
       <c r="J112" s="15"/>
       <c r="K112" s="15"/>
@@ -7411,27 +7402,27 @@
       <c r="P112" s="15"/>
     </row>
     <row r="113" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A113" s="43"/>
+      <c r="A113" s="42"/>
       <c r="B113" s="24">
         <v>200</v>
       </c>
       <c r="C113" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D113" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="D113" s="30" t="s">
+      <c r="E113" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="E113" s="30" t="s">
+      <c r="F113" s="30" t="s">
         <v>267</v>
-      </c>
-      <c r="F113" s="30" t="s">
-        <v>268</v>
       </c>
       <c r="G113" s="26" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H113" s="43"/>
+      <c r="H113" s="42"/>
       <c r="I113" s="15"/>
       <c r="J113" s="15"/>
       <c r="K113" s="15"/>
@@ -7442,27 +7433,27 @@
       <c r="P113" s="15"/>
     </row>
     <row r="114" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A114" s="43"/>
+      <c r="A114" s="42"/>
       <c r="B114" s="24">
         <v>500</v>
       </c>
       <c r="C114" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="D114" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="D114" s="30" t="s">
+      <c r="E114" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="E114" s="30" t="s">
+      <c r="F114" s="30" t="s">
         <v>271</v>
-      </c>
-      <c r="F114" s="30" t="s">
-        <v>272</v>
       </c>
       <c r="G114" s="26" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H114" s="43"/>
+      <c r="H114" s="42"/>
       <c r="I114" s="15"/>
       <c r="J114" s="15"/>
       <c r="K114" s="15"/>
@@ -7473,27 +7464,27 @@
       <c r="P114" s="15"/>
     </row>
     <row r="115" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A115" s="44"/>
+      <c r="A115" s="43"/>
       <c r="B115" s="24">
         <v>1000</v>
       </c>
       <c r="C115" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D115" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="D115" s="30" t="s">
+      <c r="E115" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="E115" s="30" t="s">
+      <c r="F115" s="30" t="s">
         <v>275</v>
-      </c>
-      <c r="F115" s="30" t="s">
-        <v>276</v>
       </c>
       <c r="G115" s="26" t="e">
         <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H115" s="43"/>
+      <c r="H115" s="42"/>
       <c r="I115" s="15"/>
       <c r="J115" s="15"/>
       <c r="K115" s="15"/>
@@ -7504,29 +7495,29 @@
       <c r="P115" s="15"/>
     </row>
     <row r="116" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A116" s="35">
+      <c r="A116" s="39">
         <v>2</v>
       </c>
       <c r="B116" s="22">
         <v>5</v>
       </c>
       <c r="C116" s="30" t="s">
+        <v>560</v>
+      </c>
+      <c r="D116" s="30" t="s">
         <v>561</v>
       </c>
-      <c r="D116" s="30" t="s">
+      <c r="E116" s="30" t="s">
         <v>562</v>
       </c>
-      <c r="E116" s="30" t="s">
+      <c r="F116" s="30" t="s">
         <v>563</v>
-      </c>
-      <c r="F116" s="30" t="s">
-        <v>564</v>
       </c>
       <c r="G116" s="26" t="e">
         <f t="shared" ref="G116:G139" si="9">20*LOG10((E116/F116)/(C116/D116))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H116" s="43"/>
+      <c r="H116" s="42"/>
       <c r="I116" s="15"/>
       <c r="J116" s="15"/>
       <c r="K116" s="15"/>
@@ -7537,27 +7528,27 @@
       <c r="P116" s="15"/>
     </row>
     <row r="117" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A117" s="35"/>
+      <c r="A117" s="39"/>
       <c r="B117" s="22">
         <v>10</v>
       </c>
       <c r="C117" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="D117" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="D117" s="30" t="s">
+      <c r="E117" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="E117" s="30" t="s">
+      <c r="F117" s="30" t="s">
         <v>279</v>
-      </c>
-      <c r="F117" s="30" t="s">
-        <v>280</v>
       </c>
       <c r="G117" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H117" s="43"/>
+      <c r="H117" s="42"/>
       <c r="I117" s="15"/>
       <c r="J117" s="15"/>
       <c r="K117" s="15"/>
@@ -7568,27 +7559,27 @@
       <c r="P117" s="15"/>
     </row>
     <row r="118" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A118" s="35"/>
+      <c r="A118" s="39"/>
       <c r="B118" s="23">
         <v>20</v>
       </c>
       <c r="C118" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="D118" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="D118" s="30" t="s">
+      <c r="E118" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="E118" s="30" t="s">
+      <c r="F118" s="30" t="s">
         <v>283</v>
-      </c>
-      <c r="F118" s="30" t="s">
-        <v>284</v>
       </c>
       <c r="G118" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H118" s="43"/>
+      <c r="H118" s="42"/>
       <c r="I118" s="15"/>
       <c r="J118" s="15"/>
       <c r="K118" s="15"/>
@@ -7599,27 +7590,27 @@
       <c r="P118" s="15"/>
     </row>
     <row r="119" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A119" s="35"/>
+      <c r="A119" s="39"/>
       <c r="B119" s="23">
         <v>50</v>
       </c>
       <c r="C119" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="D119" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="D119" s="30" t="s">
+      <c r="E119" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="E119" s="30" t="s">
+      <c r="F119" s="30" t="s">
         <v>287</v>
-      </c>
-      <c r="F119" s="30" t="s">
-        <v>288</v>
       </c>
       <c r="G119" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H119" s="43"/>
+      <c r="H119" s="42"/>
       <c r="I119" s="15"/>
       <c r="J119" s="15"/>
       <c r="K119" s="15"/>
@@ -7630,27 +7621,27 @@
       <c r="P119" s="15"/>
     </row>
     <row r="120" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A120" s="35"/>
+      <c r="A120" s="39"/>
       <c r="B120" s="23">
         <v>100</v>
       </c>
       <c r="C120" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="D120" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D120" s="30" t="s">
+      <c r="E120" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="E120" s="30" t="s">
+      <c r="F120" s="30" t="s">
         <v>291</v>
-      </c>
-      <c r="F120" s="30" t="s">
-        <v>292</v>
       </c>
       <c r="G120" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H120" s="43"/>
+      <c r="H120" s="42"/>
       <c r="I120" s="15"/>
       <c r="J120" s="15"/>
       <c r="K120" s="15"/>
@@ -7661,27 +7652,27 @@
       <c r="P120" s="15"/>
     </row>
     <row r="121" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A121" s="35"/>
+      <c r="A121" s="39"/>
       <c r="B121" s="24">
         <v>200</v>
       </c>
       <c r="C121" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="D121" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="D121" s="30" t="s">
+      <c r="E121" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="E121" s="30" t="s">
+      <c r="F121" s="30" t="s">
         <v>295</v>
-      </c>
-      <c r="F121" s="30" t="s">
-        <v>296</v>
       </c>
       <c r="G121" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H121" s="43"/>
+      <c r="H121" s="42"/>
       <c r="I121" s="15"/>
       <c r="J121" s="15"/>
       <c r="K121" s="15"/>
@@ -7692,27 +7683,27 @@
       <c r="P121" s="15"/>
     </row>
     <row r="122" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A122" s="35"/>
+      <c r="A122" s="39"/>
       <c r="B122" s="24">
         <v>500</v>
       </c>
       <c r="C122" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="D122" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="D122" s="30" t="s">
+      <c r="E122" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="E122" s="30" t="s">
+      <c r="F122" s="30" t="s">
         <v>299</v>
-      </c>
-      <c r="F122" s="30" t="s">
-        <v>300</v>
       </c>
       <c r="G122" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H122" s="43"/>
+      <c r="H122" s="42"/>
       <c r="I122" s="15"/>
       <c r="J122" s="15"/>
       <c r="K122" s="15"/>
@@ -7723,27 +7714,27 @@
       <c r="P122" s="15"/>
     </row>
     <row r="123" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A123" s="35"/>
+      <c r="A123" s="39"/>
       <c r="B123" s="24">
         <v>1000</v>
       </c>
       <c r="C123" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="D123" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="D123" s="30" t="s">
+      <c r="E123" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="E123" s="30" t="s">
+      <c r="F123" s="30" t="s">
         <v>303</v>
-      </c>
-      <c r="F123" s="30" t="s">
-        <v>304</v>
       </c>
       <c r="G123" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H123" s="43"/>
+      <c r="H123" s="42"/>
       <c r="I123" s="15"/>
       <c r="J123" s="15"/>
       <c r="K123" s="15"/>
@@ -7754,29 +7745,29 @@
       <c r="P123" s="15"/>
     </row>
     <row r="124" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A124" s="35">
+      <c r="A124" s="39">
         <v>3</v>
       </c>
       <c r="B124" s="22">
         <v>5</v>
       </c>
       <c r="C124" s="30" t="s">
+        <v>564</v>
+      </c>
+      <c r="D124" s="30" t="s">
         <v>565</v>
       </c>
-      <c r="D124" s="30" t="s">
+      <c r="E124" s="30" t="s">
         <v>566</v>
       </c>
-      <c r="E124" s="30" t="s">
+      <c r="F124" s="30" t="s">
         <v>567</v>
-      </c>
-      <c r="F124" s="30" t="s">
-        <v>568</v>
       </c>
       <c r="G124" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H124" s="43"/>
+      <c r="H124" s="42"/>
       <c r="I124" s="15"/>
       <c r="J124" s="15"/>
       <c r="K124" s="15"/>
@@ -7787,27 +7778,27 @@
       <c r="P124" s="15"/>
     </row>
     <row r="125" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A125" s="35"/>
+      <c r="A125" s="39"/>
       <c r="B125" s="22">
         <v>10</v>
       </c>
       <c r="C125" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D125" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="D125" s="30" t="s">
+      <c r="E125" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="E125" s="30" t="s">
+      <c r="F125" s="30" t="s">
         <v>307</v>
-      </c>
-      <c r="F125" s="30" t="s">
-        <v>308</v>
       </c>
       <c r="G125" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H125" s="43"/>
+      <c r="H125" s="42"/>
       <c r="I125" s="15"/>
       <c r="J125" s="15"/>
       <c r="K125" s="15"/>
@@ -7818,27 +7809,27 @@
       <c r="P125" s="15"/>
     </row>
     <row r="126" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A126" s="35"/>
+      <c r="A126" s="39"/>
       <c r="B126" s="23">
         <v>20</v>
       </c>
       <c r="C126" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="D126" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="D126" s="30" t="s">
+      <c r="E126" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="E126" s="30" t="s">
+      <c r="F126" s="30" t="s">
         <v>311</v>
-      </c>
-      <c r="F126" s="30" t="s">
-        <v>312</v>
       </c>
       <c r="G126" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H126" s="43"/>
+      <c r="H126" s="42"/>
       <c r="I126" s="15"/>
       <c r="J126" s="15"/>
       <c r="K126" s="15"/>
@@ -7849,27 +7840,27 @@
       <c r="P126" s="15"/>
     </row>
     <row r="127" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A127" s="35"/>
+      <c r="A127" s="39"/>
       <c r="B127" s="23">
         <v>50</v>
       </c>
       <c r="C127" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D127" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="D127" s="30" t="s">
+      <c r="E127" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="E127" s="30" t="s">
+      <c r="F127" s="30" t="s">
         <v>315</v>
-      </c>
-      <c r="F127" s="30" t="s">
-        <v>316</v>
       </c>
       <c r="G127" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H127" s="43"/>
+      <c r="H127" s="42"/>
       <c r="I127" s="15"/>
       <c r="J127" s="15"/>
       <c r="K127" s="15"/>
@@ -7880,27 +7871,27 @@
       <c r="P127" s="15"/>
     </row>
     <row r="128" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A128" s="35"/>
+      <c r="A128" s="39"/>
       <c r="B128" s="23">
         <v>100</v>
       </c>
       <c r="C128" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="D128" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="D128" s="30" t="s">
+      <c r="E128" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="E128" s="30" t="s">
+      <c r="F128" s="30" t="s">
         <v>319</v>
-      </c>
-      <c r="F128" s="30" t="s">
-        <v>320</v>
       </c>
       <c r="G128" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H128" s="43"/>
+      <c r="H128" s="42"/>
       <c r="I128" s="15"/>
       <c r="J128" s="15"/>
       <c r="K128" s="15"/>
@@ -7911,27 +7902,27 @@
       <c r="P128" s="15"/>
     </row>
     <row r="129" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A129" s="35"/>
+      <c r="A129" s="39"/>
       <c r="B129" s="24">
         <v>200</v>
       </c>
       <c r="C129" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="D129" s="30" t="s">
         <v>321</v>
       </c>
-      <c r="D129" s="30" t="s">
+      <c r="E129" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="E129" s="30" t="s">
+      <c r="F129" s="30" t="s">
         <v>323</v>
-      </c>
-      <c r="F129" s="30" t="s">
-        <v>324</v>
       </c>
       <c r="G129" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H129" s="43"/>
+      <c r="H129" s="42"/>
       <c r="I129" s="15"/>
       <c r="J129" s="15"/>
       <c r="K129" s="15"/>
@@ -7942,27 +7933,27 @@
       <c r="P129" s="15"/>
     </row>
     <row r="130" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A130" s="35"/>
+      <c r="A130" s="39"/>
       <c r="B130" s="24">
         <v>500</v>
       </c>
       <c r="C130" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="D130" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="D130" s="30" t="s">
+      <c r="E130" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="E130" s="30" t="s">
+      <c r="F130" s="30" t="s">
         <v>327</v>
-      </c>
-      <c r="F130" s="30" t="s">
-        <v>328</v>
       </c>
       <c r="G130" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H130" s="43"/>
+      <c r="H130" s="42"/>
       <c r="I130" s="15"/>
       <c r="J130" s="15"/>
       <c r="K130" s="15"/>
@@ -7973,27 +7964,27 @@
       <c r="P130" s="15"/>
     </row>
     <row r="131" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A131" s="35"/>
+      <c r="A131" s="39"/>
       <c r="B131" s="24">
         <v>1000</v>
       </c>
       <c r="C131" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="D131" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="D131" s="30" t="s">
+      <c r="E131" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="E131" s="30" t="s">
+      <c r="F131" s="30" t="s">
         <v>331</v>
-      </c>
-      <c r="F131" s="30" t="s">
-        <v>332</v>
       </c>
       <c r="G131" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H131" s="43"/>
+      <c r="H131" s="42"/>
       <c r="I131" s="15"/>
       <c r="J131" s="15"/>
       <c r="K131" s="15"/>
@@ -8004,29 +7995,29 @@
       <c r="P131" s="15"/>
     </row>
     <row r="132" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A132" s="35">
+      <c r="A132" s="39">
         <v>4</v>
       </c>
       <c r="B132" s="22">
         <v>5</v>
       </c>
       <c r="C132" s="30" t="s">
+        <v>568</v>
+      </c>
+      <c r="D132" s="30" t="s">
         <v>569</v>
       </c>
-      <c r="D132" s="30" t="s">
+      <c r="E132" s="30" t="s">
         <v>570</v>
       </c>
-      <c r="E132" s="30" t="s">
+      <c r="F132" s="30" t="s">
         <v>571</v>
-      </c>
-      <c r="F132" s="30" t="s">
-        <v>572</v>
       </c>
       <c r="G132" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H132" s="43"/>
+      <c r="H132" s="42"/>
       <c r="I132" s="15"/>
       <c r="J132" s="15"/>
       <c r="K132" s="15"/>
@@ -8037,27 +8028,27 @@
       <c r="P132" s="15"/>
     </row>
     <row r="133" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A133" s="35"/>
+      <c r="A133" s="39"/>
       <c r="B133" s="22">
         <v>10</v>
       </c>
       <c r="C133" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D133" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="D133" s="30" t="s">
+      <c r="E133" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="E133" s="30" t="s">
+      <c r="F133" s="30" t="s">
         <v>335</v>
-      </c>
-      <c r="F133" s="30" t="s">
-        <v>336</v>
       </c>
       <c r="G133" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H133" s="43"/>
+      <c r="H133" s="42"/>
       <c r="I133" s="15"/>
       <c r="J133" s="15"/>
       <c r="K133" s="15"/>
@@ -8068,27 +8059,27 @@
       <c r="P133" s="15"/>
     </row>
     <row r="134" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A134" s="35"/>
+      <c r="A134" s="39"/>
       <c r="B134" s="23">
         <v>20</v>
       </c>
       <c r="C134" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="D134" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="D134" s="30" t="s">
+      <c r="E134" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="E134" s="30" t="s">
+      <c r="F134" s="30" t="s">
         <v>339</v>
-      </c>
-      <c r="F134" s="30" t="s">
-        <v>340</v>
       </c>
       <c r="G134" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H134" s="43"/>
+      <c r="H134" s="42"/>
       <c r="I134" s="15"/>
       <c r="J134" s="15"/>
       <c r="K134" s="15"/>
@@ -8099,27 +8090,27 @@
       <c r="P134" s="15"/>
     </row>
     <row r="135" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A135" s="35"/>
+      <c r="A135" s="39"/>
       <c r="B135" s="23">
         <v>50</v>
       </c>
       <c r="C135" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="D135" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="D135" s="30" t="s">
+      <c r="E135" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="E135" s="30" t="s">
+      <c r="F135" s="30" t="s">
         <v>343</v>
-      </c>
-      <c r="F135" s="30" t="s">
-        <v>344</v>
       </c>
       <c r="G135" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H135" s="43"/>
+      <c r="H135" s="42"/>
       <c r="I135" s="15"/>
       <c r="J135" s="15"/>
       <c r="K135" s="15"/>
@@ -8130,27 +8121,27 @@
       <c r="P135" s="15"/>
     </row>
     <row r="136" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A136" s="35"/>
+      <c r="A136" s="39"/>
       <c r="B136" s="23">
         <v>100</v>
       </c>
       <c r="C136" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="D136" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="D136" s="30" t="s">
+      <c r="E136" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="E136" s="30" t="s">
+      <c r="F136" s="30" t="s">
         <v>347</v>
-      </c>
-      <c r="F136" s="30" t="s">
-        <v>348</v>
       </c>
       <c r="G136" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H136" s="43"/>
+      <c r="H136" s="42"/>
       <c r="I136" s="15"/>
       <c r="J136" s="15"/>
       <c r="K136" s="15"/>
@@ -8161,27 +8152,27 @@
       <c r="P136" s="15"/>
     </row>
     <row r="137" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A137" s="35"/>
+      <c r="A137" s="39"/>
       <c r="B137" s="24">
         <v>200</v>
       </c>
       <c r="C137" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="D137" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="D137" s="30" t="s">
+      <c r="E137" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="E137" s="30" t="s">
+      <c r="F137" s="30" t="s">
         <v>351</v>
-      </c>
-      <c r="F137" s="30" t="s">
-        <v>352</v>
       </c>
       <c r="G137" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H137" s="43"/>
+      <c r="H137" s="42"/>
       <c r="I137" s="15"/>
       <c r="J137" s="15"/>
       <c r="K137" s="15"/>
@@ -8192,27 +8183,27 @@
       <c r="P137" s="15"/>
     </row>
     <row r="138" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A138" s="35"/>
+      <c r="A138" s="39"/>
       <c r="B138" s="24">
         <v>500</v>
       </c>
       <c r="C138" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="D138" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="D138" s="30" t="s">
+      <c r="E138" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="E138" s="30" t="s">
+      <c r="F138" s="30" t="s">
         <v>355</v>
-      </c>
-      <c r="F138" s="30" t="s">
-        <v>356</v>
       </c>
       <c r="G138" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H138" s="43"/>
+      <c r="H138" s="42"/>
       <c r="I138" s="15"/>
       <c r="J138" s="15"/>
       <c r="K138" s="15"/>
@@ -8223,27 +8214,27 @@
       <c r="P138" s="15"/>
     </row>
     <row r="139" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A139" s="35"/>
+      <c r="A139" s="39"/>
       <c r="B139" s="24">
         <v>1000</v>
       </c>
       <c r="C139" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="D139" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="D139" s="30" t="s">
+      <c r="E139" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="E139" s="30" t="s">
+      <c r="F139" s="30" t="s">
         <v>359</v>
-      </c>
-      <c r="F139" s="30" t="s">
-        <v>360</v>
       </c>
       <c r="G139" s="26" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H139" s="44"/>
+      <c r="H139" s="43"/>
       <c r="I139" s="15"/>
       <c r="J139" s="15"/>
       <c r="K139" s="15"/>
@@ -8272,21 +8263,21 @@
       <c r="P140" s="15"/>
     </row>
     <row r="141" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="53" t="s">
+      <c r="A141" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="B141" s="53"/>
-      <c r="C141" s="53"/>
-      <c r="D141" s="53"/>
-      <c r="E141" s="53"/>
-      <c r="F141" s="53"/>
-      <c r="G141" s="53"/>
-      <c r="H141" s="53"/>
-      <c r="I141" s="53"/>
-      <c r="J141" s="53"/>
-      <c r="K141" s="53"/>
-      <c r="L141" s="53"/>
-      <c r="M141" s="53"/>
+      <c r="B141" s="55"/>
+      <c r="C141" s="55"/>
+      <c r="D141" s="55"/>
+      <c r="E141" s="55"/>
+      <c r="F141" s="55"/>
+      <c r="G141" s="55"/>
+      <c r="H141" s="55"/>
+      <c r="I141" s="55"/>
+      <c r="J141" s="55"/>
+      <c r="K141" s="55"/>
+      <c r="L141" s="55"/>
+      <c r="M141" s="55"/>
       <c r="N141" s="15"/>
       <c r="O141" s="15"/>
       <c r="P141" s="15"/>
@@ -8310,18 +8301,18 @@
       <c r="P142" s="15"/>
     </row>
     <row r="143" spans="1:16" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="54" t="s">
+      <c r="A143" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="B143" s="54"/>
-      <c r="C143" s="35" t="s">
+      <c r="B143" s="56"/>
+      <c r="C143" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D143" s="35"/>
-      <c r="E143" s="38" t="s">
+      <c r="D143" s="39"/>
+      <c r="E143" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="F143" s="38"/>
+      <c r="F143" s="47"/>
       <c r="G143" s="15"/>
       <c r="H143" s="15"/>
       <c r="I143" s="15"/>
@@ -8334,19 +8325,19 @@
       <c r="P143" s="15"/>
     </row>
     <row r="144" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="40">
+      <c r="A144" s="57">
         <v>15.43</v>
       </c>
-      <c r="B144" s="40"/>
-      <c r="C144" s="66">
+      <c r="B144" s="57"/>
+      <c r="C144" s="58">
         <f>(A144-20)/10000000</f>
         <v>-4.5700000000000003E-7</v>
       </c>
-      <c r="D144" s="66"/>
-      <c r="E144" s="38" t="s">
+      <c r="D144" s="58"/>
+      <c r="E144" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="F144" s="38"/>
+      <c r="F144" s="47"/>
       <c r="G144" s="15"/>
       <c r="H144" s="15"/>
       <c r="I144" s="15"/>
@@ -8453,1346 +8444,1346 @@
       <c r="P149" s="15"/>
     </row>
     <row r="150" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="38" t="s">
+      <c r="A150" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B150" s="38" t="s">
+      <c r="B150" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C150" s="38"/>
-      <c r="D150" s="38" t="s">
+      <c r="C150" s="47"/>
+      <c r="D150" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E150" s="38" t="s">
+      <c r="E150" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="F150" s="38"/>
-      <c r="G150" s="38" t="s">
+      <c r="F150" s="47"/>
+      <c r="G150" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38" t="s">
+      <c r="H150" s="47"/>
+      <c r="I150" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="J150" s="38" t="s">
+      <c r="J150" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="K150" s="38"/>
-      <c r="L150" s="38" t="s">
+      <c r="K150" s="47"/>
+      <c r="L150" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="M150" s="38"/>
-      <c r="N150" s="38" t="s">
+      <c r="M150" s="47"/>
+      <c r="N150" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="O150" s="38" t="s">
+      <c r="O150" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="P150" s="41" t="s">
+      <c r="P150" s="65" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="151" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="38"/>
-      <c r="B151" s="38"/>
-      <c r="C151" s="38"/>
-      <c r="D151" s="38"/>
-      <c r="E151" s="38"/>
-      <c r="F151" s="38"/>
-      <c r="G151" s="38"/>
-      <c r="H151" s="38"/>
-      <c r="I151" s="38"/>
-      <c r="J151" s="38"/>
-      <c r="K151" s="38"/>
-      <c r="L151" s="38"/>
-      <c r="M151" s="38"/>
-      <c r="N151" s="38"/>
-      <c r="O151" s="38"/>
-      <c r="P151" s="38"/>
+      <c r="A151" s="47"/>
+      <c r="B151" s="47"/>
+      <c r="C151" s="47"/>
+      <c r="D151" s="47"/>
+      <c r="E151" s="47"/>
+      <c r="F151" s="47"/>
+      <c r="G151" s="47"/>
+      <c r="H151" s="47"/>
+      <c r="I151" s="47"/>
+      <c r="J151" s="47"/>
+      <c r="K151" s="47"/>
+      <c r="L151" s="47"/>
+      <c r="M151" s="47"/>
+      <c r="N151" s="47"/>
+      <c r="O151" s="47"/>
+      <c r="P151" s="47"/>
     </row>
     <row r="152" spans="1:16" s="1" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="38"/>
-      <c r="B152" s="38"/>
-      <c r="C152" s="38"/>
-      <c r="D152" s="38"/>
-      <c r="E152" s="38"/>
-      <c r="F152" s="38"/>
-      <c r="G152" s="38"/>
-      <c r="H152" s="38"/>
-      <c r="I152" s="38"/>
-      <c r="J152" s="38"/>
-      <c r="K152" s="38"/>
-      <c r="L152" s="38"/>
-      <c r="M152" s="38"/>
-      <c r="N152" s="38"/>
-      <c r="O152" s="38"/>
-      <c r="P152" s="38"/>
+      <c r="A152" s="47"/>
+      <c r="B152" s="47"/>
+      <c r="C152" s="47"/>
+      <c r="D152" s="47"/>
+      <c r="E152" s="47"/>
+      <c r="F152" s="47"/>
+      <c r="G152" s="47"/>
+      <c r="H152" s="47"/>
+      <c r="I152" s="47"/>
+      <c r="J152" s="47"/>
+      <c r="K152" s="47"/>
+      <c r="L152" s="47"/>
+      <c r="M152" s="47"/>
+      <c r="N152" s="47"/>
+      <c r="O152" s="47"/>
+      <c r="P152" s="47"/>
     </row>
     <row r="153" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="35">
+      <c r="A153" s="39">
         <v>1</v>
       </c>
-      <c r="B153" s="35">
+      <c r="B153" s="39">
         <v>5</v>
       </c>
-      <c r="C153" s="35"/>
+      <c r="C153" s="39"/>
       <c r="D153" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E153" s="40" t="s">
+      <c r="E153" s="57" t="s">
+        <v>576</v>
+      </c>
+      <c r="F153" s="57"/>
+      <c r="G153" s="57" t="s">
         <v>577</v>
       </c>
-      <c r="F153" s="40"/>
-      <c r="G153" s="40" t="s">
+      <c r="H153" s="57"/>
+      <c r="I153" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="H153" s="40"/>
-      <c r="I153" s="29" t="s">
+      <c r="J153" s="57" t="s">
         <v>579</v>
       </c>
-      <c r="J153" s="40" t="s">
+      <c r="K153" s="57"/>
+      <c r="L153" s="57" t="s">
         <v>580</v>
       </c>
-      <c r="K153" s="40"/>
-      <c r="L153" s="40" t="s">
+      <c r="M153" s="57"/>
+      <c r="N153" s="29" t="s">
         <v>581</v>
-      </c>
-      <c r="M153" s="40"/>
-      <c r="N153" s="29" t="s">
-        <v>582</v>
       </c>
       <c r="O153" s="26" t="e">
         <f>IF(ABS(((J153-N153)/(E153-I153)-1)*100)&gt;ABS(((L153-N153)/(G153-I153)-1)*100),((J153-N153)/(E153-I153)-1)*100,((L153-N153)/(G153-I153)-1)*100)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P153" s="35" t="s">
+      <c r="P153" s="39" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="154" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="35"/>
-      <c r="B154" s="35">
+      <c r="A154" s="39"/>
+      <c r="B154" s="39">
         <v>10</v>
       </c>
-      <c r="C154" s="35"/>
+      <c r="C154" s="39"/>
       <c r="D154" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E154" s="40" t="s">
+      <c r="E154" s="57" t="s">
+        <v>360</v>
+      </c>
+      <c r="F154" s="57"/>
+      <c r="G154" s="57" t="s">
         <v>361</v>
       </c>
-      <c r="F154" s="40"/>
-      <c r="G154" s="40" t="s">
+      <c r="H154" s="57"/>
+      <c r="I154" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="H154" s="40"/>
-      <c r="I154" s="34" t="s">
+      <c r="J154" s="57" t="s">
         <v>363</v>
       </c>
-      <c r="J154" s="40" t="s">
+      <c r="K154" s="57"/>
+      <c r="L154" s="57" t="s">
         <v>364</v>
       </c>
-      <c r="K154" s="40"/>
-      <c r="L154" s="40" t="s">
+      <c r="M154" s="57"/>
+      <c r="N154" s="34" t="s">
         <v>365</v>
-      </c>
-      <c r="M154" s="40"/>
-      <c r="N154" s="34" t="s">
-        <v>366</v>
       </c>
       <c r="O154" s="26" t="e">
         <f t="shared" ref="O154:O183" si="10">IF(ABS(((J154-N154)/(E154-I154)-1)*100)&gt;ABS(((L154-N154)/(G154-I154)-1)*100),((J154-N154)/(E154-I154)-1)*100,((L154-N154)/(G154-I154)-1)*100)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P154" s="35"/>
+      <c r="P154" s="39"/>
     </row>
     <row r="155" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="35"/>
-      <c r="B155" s="35">
+      <c r="A155" s="39"/>
+      <c r="B155" s="39">
         <v>20</v>
       </c>
-      <c r="C155" s="35"/>
+      <c r="C155" s="39"/>
       <c r="D155" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E155" s="40" t="s">
+      <c r="E155" s="57" t="s">
+        <v>366</v>
+      </c>
+      <c r="F155" s="57"/>
+      <c r="G155" s="57" t="s">
         <v>367</v>
       </c>
-      <c r="F155" s="40"/>
-      <c r="G155" s="40" t="s">
+      <c r="H155" s="57"/>
+      <c r="I155" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="H155" s="40"/>
-      <c r="I155" s="34" t="s">
+      <c r="J155" s="57" t="s">
         <v>369</v>
       </c>
-      <c r="J155" s="40" t="s">
+      <c r="K155" s="57"/>
+      <c r="L155" s="57" t="s">
         <v>370</v>
       </c>
-      <c r="K155" s="40"/>
-      <c r="L155" s="40" t="s">
+      <c r="M155" s="57"/>
+      <c r="N155" s="34" t="s">
         <v>371</v>
-      </c>
-      <c r="M155" s="40"/>
-      <c r="N155" s="34" t="s">
-        <v>372</v>
       </c>
       <c r="O155" s="26" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P155" s="35"/>
+      <c r="P155" s="39"/>
     </row>
     <row r="156" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="35"/>
-      <c r="B156" s="35">
+      <c r="A156" s="39"/>
+      <c r="B156" s="39">
         <v>50</v>
       </c>
-      <c r="C156" s="35"/>
+      <c r="C156" s="39"/>
       <c r="D156" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E156" s="40" t="s">
+      <c r="E156" s="57" t="s">
+        <v>372</v>
+      </c>
+      <c r="F156" s="57"/>
+      <c r="G156" s="57" t="s">
         <v>373</v>
       </c>
-      <c r="F156" s="40"/>
-      <c r="G156" s="40" t="s">
+      <c r="H156" s="57"/>
+      <c r="I156" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="H156" s="40"/>
-      <c r="I156" s="34" t="s">
+      <c r="J156" s="57" t="s">
         <v>375</v>
       </c>
-      <c r="J156" s="40" t="s">
+      <c r="K156" s="57"/>
+      <c r="L156" s="57" t="s">
         <v>376</v>
       </c>
-      <c r="K156" s="40"/>
-      <c r="L156" s="40" t="s">
+      <c r="M156" s="57"/>
+      <c r="N156" s="34" t="s">
         <v>377</v>
-      </c>
-      <c r="M156" s="40"/>
-      <c r="N156" s="34" t="s">
-        <v>378</v>
       </c>
       <c r="O156" s="26" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P156" s="35"/>
+      <c r="P156" s="39"/>
     </row>
     <row r="157" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="35"/>
-      <c r="B157" s="35">
+      <c r="A157" s="39"/>
+      <c r="B157" s="39">
         <v>100</v>
       </c>
-      <c r="C157" s="35"/>
+      <c r="C157" s="39"/>
       <c r="D157" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E157" s="40" t="s">
+      <c r="E157" s="57" t="s">
+        <v>378</v>
+      </c>
+      <c r="F157" s="57"/>
+      <c r="G157" s="57" t="s">
         <v>379</v>
       </c>
-      <c r="F157" s="40"/>
-      <c r="G157" s="40" t="s">
+      <c r="H157" s="57"/>
+      <c r="I157" s="34" t="s">
         <v>380</v>
       </c>
-      <c r="H157" s="40"/>
-      <c r="I157" s="34" t="s">
+      <c r="J157" s="57" t="s">
         <v>381</v>
       </c>
-      <c r="J157" s="40" t="s">
+      <c r="K157" s="57"/>
+      <c r="L157" s="57" t="s">
         <v>382</v>
       </c>
-      <c r="K157" s="40"/>
-      <c r="L157" s="40" t="s">
+      <c r="M157" s="57"/>
+      <c r="N157" s="34" t="s">
         <v>383</v>
-      </c>
-      <c r="M157" s="40"/>
-      <c r="N157" s="34" t="s">
-        <v>384</v>
       </c>
       <c r="O157" s="26" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P157" s="35"/>
+      <c r="P157" s="39"/>
     </row>
     <row r="158" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="35"/>
-      <c r="B158" s="35">
+      <c r="A158" s="39"/>
+      <c r="B158" s="39">
         <v>200</v>
       </c>
-      <c r="C158" s="35"/>
+      <c r="C158" s="39"/>
       <c r="D158" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E158" s="40" t="s">
+      <c r="E158" s="57" t="s">
+        <v>384</v>
+      </c>
+      <c r="F158" s="57"/>
+      <c r="G158" s="57" t="s">
         <v>385</v>
       </c>
-      <c r="F158" s="40"/>
-      <c r="G158" s="40" t="s">
+      <c r="H158" s="57"/>
+      <c r="I158" s="34" t="s">
         <v>386</v>
       </c>
-      <c r="H158" s="40"/>
-      <c r="I158" s="34" t="s">
+      <c r="J158" s="57" t="s">
         <v>387</v>
       </c>
-      <c r="J158" s="40" t="s">
+      <c r="K158" s="57"/>
+      <c r="L158" s="57" t="s">
         <v>388</v>
       </c>
-      <c r="K158" s="40"/>
-      <c r="L158" s="40" t="s">
+      <c r="M158" s="57"/>
+      <c r="N158" s="34" t="s">
         <v>389</v>
-      </c>
-      <c r="M158" s="40"/>
-      <c r="N158" s="34" t="s">
-        <v>390</v>
       </c>
       <c r="O158" s="26" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P158" s="35"/>
+      <c r="P158" s="39"/>
     </row>
     <row r="159" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="35"/>
-      <c r="B159" s="35">
+      <c r="A159" s="39"/>
+      <c r="B159" s="39">
         <v>500</v>
       </c>
-      <c r="C159" s="35"/>
+      <c r="C159" s="39"/>
       <c r="D159" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E159" s="40" t="s">
+      <c r="E159" s="57" t="s">
+        <v>390</v>
+      </c>
+      <c r="F159" s="57"/>
+      <c r="G159" s="57" t="s">
         <v>391</v>
       </c>
-      <c r="F159" s="40"/>
-      <c r="G159" s="40" t="s">
+      <c r="H159" s="57"/>
+      <c r="I159" s="34" t="s">
         <v>392</v>
       </c>
-      <c r="H159" s="40"/>
-      <c r="I159" s="34" t="s">
+      <c r="J159" s="57" t="s">
         <v>393</v>
       </c>
-      <c r="J159" s="40" t="s">
+      <c r="K159" s="57"/>
+      <c r="L159" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="K159" s="40"/>
-      <c r="L159" s="40" t="s">
+      <c r="M159" s="57"/>
+      <c r="N159" s="34" t="s">
         <v>395</v>
-      </c>
-      <c r="M159" s="40"/>
-      <c r="N159" s="34" t="s">
-        <v>396</v>
       </c>
       <c r="O159" s="26" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P159" s="35"/>
+      <c r="P159" s="39"/>
     </row>
     <row r="160" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="35"/>
-      <c r="B160" s="35">
+      <c r="A160" s="39"/>
+      <c r="B160" s="39">
         <v>1000</v>
       </c>
-      <c r="C160" s="35"/>
+      <c r="C160" s="39"/>
       <c r="D160" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E160" s="40" t="s">
+      <c r="E160" s="57" t="s">
+        <v>396</v>
+      </c>
+      <c r="F160" s="57"/>
+      <c r="G160" s="57" t="s">
         <v>397</v>
       </c>
-      <c r="F160" s="40"/>
-      <c r="G160" s="40" t="s">
+      <c r="H160" s="57"/>
+      <c r="I160" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="H160" s="40"/>
-      <c r="I160" s="34" t="s">
+      <c r="J160" s="57" t="s">
         <v>399</v>
       </c>
-      <c r="J160" s="40" t="s">
+      <c r="K160" s="57"/>
+      <c r="L160" s="57" t="s">
         <v>400</v>
       </c>
-      <c r="K160" s="40"/>
-      <c r="L160" s="40" t="s">
+      <c r="M160" s="57"/>
+      <c r="N160" s="34" t="s">
         <v>401</v>
-      </c>
-      <c r="M160" s="40"/>
-      <c r="N160" s="34" t="s">
-        <v>402</v>
       </c>
       <c r="O160" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P160" s="35"/>
+      <c r="P160" s="39"/>
     </row>
     <row r="161" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="35">
+      <c r="A161" s="39">
         <v>2</v>
       </c>
-      <c r="B161" s="35">
+      <c r="B161" s="39">
         <v>5</v>
       </c>
-      <c r="C161" s="35"/>
+      <c r="C161" s="39"/>
       <c r="D161" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E161" s="40" t="s">
+      <c r="E161" s="57" t="s">
+        <v>582</v>
+      </c>
+      <c r="F161" s="57"/>
+      <c r="G161" s="57" t="s">
         <v>583</v>
       </c>
-      <c r="F161" s="40"/>
-      <c r="G161" s="40" t="s">
+      <c r="H161" s="57"/>
+      <c r="I161" s="34" t="s">
         <v>584</v>
       </c>
-      <c r="H161" s="40"/>
-      <c r="I161" s="34" t="s">
+      <c r="J161" s="57" t="s">
         <v>585</v>
       </c>
-      <c r="J161" s="40" t="s">
+      <c r="K161" s="57"/>
+      <c r="L161" s="57" t="s">
         <v>586</v>
       </c>
-      <c r="K161" s="40"/>
-      <c r="L161" s="40" t="s">
+      <c r="M161" s="57"/>
+      <c r="N161" s="34" t="s">
         <v>587</v>
-      </c>
-      <c r="M161" s="40"/>
-      <c r="N161" s="34" t="s">
-        <v>588</v>
       </c>
       <c r="O161" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P161" s="35"/>
+      <c r="P161" s="39"/>
     </row>
     <row r="162" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="35"/>
-      <c r="B162" s="35">
+      <c r="A162" s="39"/>
+      <c r="B162" s="39">
         <v>10</v>
       </c>
-      <c r="C162" s="35"/>
+      <c r="C162" s="39"/>
       <c r="D162" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E162" s="40" t="s">
+      <c r="E162" s="57" t="s">
+        <v>402</v>
+      </c>
+      <c r="F162" s="57"/>
+      <c r="G162" s="57" t="s">
         <v>403</v>
       </c>
-      <c r="F162" s="40"/>
-      <c r="G162" s="40" t="s">
+      <c r="H162" s="57"/>
+      <c r="I162" s="34" t="s">
         <v>404</v>
       </c>
-      <c r="H162" s="40"/>
-      <c r="I162" s="34" t="s">
+      <c r="J162" s="57" t="s">
         <v>405</v>
       </c>
-      <c r="J162" s="40" t="s">
+      <c r="K162" s="57"/>
+      <c r="L162" s="57" t="s">
         <v>406</v>
       </c>
-      <c r="K162" s="40"/>
-      <c r="L162" s="40" t="s">
-        <v>407</v>
-      </c>
-      <c r="M162" s="40"/>
+      <c r="M162" s="57"/>
       <c r="N162" s="34" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="O162" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P162" s="35"/>
+      <c r="P162" s="39"/>
     </row>
     <row r="163" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="35"/>
-      <c r="B163" s="35">
+      <c r="A163" s="39"/>
+      <c r="B163" s="39">
         <v>20</v>
       </c>
-      <c r="C163" s="35"/>
+      <c r="C163" s="39"/>
       <c r="D163" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E163" s="40" t="s">
+      <c r="E163" s="57" t="s">
+        <v>407</v>
+      </c>
+      <c r="F163" s="57"/>
+      <c r="G163" s="57" t="s">
         <v>408</v>
       </c>
-      <c r="F163" s="40"/>
-      <c r="G163" s="40" t="s">
+      <c r="H163" s="57"/>
+      <c r="I163" s="34" t="s">
         <v>409</v>
       </c>
-      <c r="H163" s="40"/>
-      <c r="I163" s="34" t="s">
+      <c r="J163" s="57" t="s">
         <v>410</v>
       </c>
-      <c r="J163" s="40" t="s">
+      <c r="K163" s="57"/>
+      <c r="L163" s="57" t="s">
         <v>411</v>
       </c>
-      <c r="K163" s="40"/>
-      <c r="L163" s="40" t="s">
-        <v>412</v>
-      </c>
-      <c r="M163" s="40"/>
+      <c r="M163" s="57"/>
       <c r="N163" s="34" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O163" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P163" s="35"/>
+      <c r="P163" s="39"/>
     </row>
     <row r="164" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="35"/>
-      <c r="B164" s="35">
+      <c r="A164" s="39"/>
+      <c r="B164" s="39">
         <v>50</v>
       </c>
-      <c r="C164" s="35"/>
+      <c r="C164" s="39"/>
       <c r="D164" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E164" s="40" t="s">
+      <c r="E164" s="57" t="s">
+        <v>412</v>
+      </c>
+      <c r="F164" s="57"/>
+      <c r="G164" s="57" t="s">
         <v>413</v>
       </c>
-      <c r="F164" s="40"/>
-      <c r="G164" s="40" t="s">
+      <c r="H164" s="57"/>
+      <c r="I164" s="34" t="s">
         <v>414</v>
       </c>
-      <c r="H164" s="40"/>
-      <c r="I164" s="34" t="s">
+      <c r="J164" s="57" t="s">
         <v>415</v>
       </c>
-      <c r="J164" s="40" t="s">
+      <c r="K164" s="57"/>
+      <c r="L164" s="57" t="s">
         <v>416</v>
       </c>
-      <c r="K164" s="40"/>
-      <c r="L164" s="40" t="s">
-        <v>417</v>
-      </c>
-      <c r="M164" s="40"/>
+      <c r="M164" s="57"/>
       <c r="N164" s="34" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="O164" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P164" s="35"/>
+      <c r="P164" s="39"/>
     </row>
     <row r="165" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="35"/>
-      <c r="B165" s="35">
+      <c r="A165" s="39"/>
+      <c r="B165" s="39">
         <v>100</v>
       </c>
-      <c r="C165" s="35"/>
+      <c r="C165" s="39"/>
       <c r="D165" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E165" s="40" t="s">
+      <c r="E165" s="57" t="s">
+        <v>417</v>
+      </c>
+      <c r="F165" s="57"/>
+      <c r="G165" s="57" t="s">
         <v>418</v>
       </c>
-      <c r="F165" s="40"/>
-      <c r="G165" s="40" t="s">
+      <c r="H165" s="57"/>
+      <c r="I165" s="34" t="s">
         <v>419</v>
       </c>
-      <c r="H165" s="40"/>
-      <c r="I165" s="34" t="s">
+      <c r="J165" s="57" t="s">
         <v>420</v>
       </c>
-      <c r="J165" s="40" t="s">
+      <c r="K165" s="57"/>
+      <c r="L165" s="57" t="s">
         <v>421</v>
       </c>
-      <c r="K165" s="40"/>
-      <c r="L165" s="40" t="s">
-        <v>422</v>
-      </c>
-      <c r="M165" s="40"/>
+      <c r="M165" s="57"/>
       <c r="N165" s="34" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="O165" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P165" s="35"/>
+      <c r="P165" s="39"/>
     </row>
     <row r="166" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="35"/>
-      <c r="B166" s="35">
+      <c r="A166" s="39"/>
+      <c r="B166" s="39">
         <v>200</v>
       </c>
-      <c r="C166" s="35"/>
+      <c r="C166" s="39"/>
       <c r="D166" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E166" s="40" t="s">
+      <c r="E166" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="F166" s="57"/>
+      <c r="G166" s="57" t="s">
         <v>423</v>
       </c>
-      <c r="F166" s="40"/>
-      <c r="G166" s="40" t="s">
+      <c r="H166" s="57"/>
+      <c r="I166" s="34" t="s">
         <v>424</v>
       </c>
-      <c r="H166" s="40"/>
-      <c r="I166" s="34" t="s">
+      <c r="J166" s="57" t="s">
         <v>425</v>
       </c>
-      <c r="J166" s="40" t="s">
+      <c r="K166" s="57"/>
+      <c r="L166" s="57" t="s">
         <v>426</v>
       </c>
-      <c r="K166" s="40"/>
-      <c r="L166" s="40" t="s">
-        <v>427</v>
-      </c>
-      <c r="M166" s="40"/>
+      <c r="M166" s="57"/>
       <c r="N166" s="34" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="O166" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P166" s="35"/>
+      <c r="P166" s="39"/>
     </row>
     <row r="167" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="35"/>
-      <c r="B167" s="35">
+      <c r="A167" s="39"/>
+      <c r="B167" s="39">
         <v>500</v>
       </c>
-      <c r="C167" s="35"/>
+      <c r="C167" s="39"/>
       <c r="D167" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E167" s="40" t="s">
+      <c r="E167" s="57" t="s">
+        <v>427</v>
+      </c>
+      <c r="F167" s="57"/>
+      <c r="G167" s="57" t="s">
         <v>428</v>
       </c>
-      <c r="F167" s="40"/>
-      <c r="G167" s="40" t="s">
+      <c r="H167" s="57"/>
+      <c r="I167" s="34" t="s">
         <v>429</v>
       </c>
-      <c r="H167" s="40"/>
-      <c r="I167" s="34" t="s">
+      <c r="J167" s="57" t="s">
         <v>430</v>
       </c>
-      <c r="J167" s="40" t="s">
+      <c r="K167" s="57"/>
+      <c r="L167" s="57" t="s">
         <v>431</v>
       </c>
-      <c r="K167" s="40"/>
-      <c r="L167" s="40" t="s">
-        <v>432</v>
-      </c>
-      <c r="M167" s="40"/>
+      <c r="M167" s="57"/>
       <c r="N167" s="34" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O167" s="28" t="e">
         <f>IF(ABS(((J167-N167)/(E167-I167)-1)*100)&gt;ABS(((L167-N167)/(G167-I167)-1)*100),((J167-N167)/(E167-I167)-1)*100,((L167-N167)/(G167-I167)-1)*100)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P167" s="35"/>
+      <c r="P167" s="39"/>
     </row>
     <row r="168" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="35"/>
-      <c r="B168" s="35">
+      <c r="A168" s="39"/>
+      <c r="B168" s="39">
         <v>1000</v>
       </c>
-      <c r="C168" s="35"/>
+      <c r="C168" s="39"/>
       <c r="D168" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E168" s="40" t="s">
+      <c r="E168" s="57" t="s">
+        <v>432</v>
+      </c>
+      <c r="F168" s="57"/>
+      <c r="G168" s="57" t="s">
         <v>433</v>
       </c>
-      <c r="F168" s="40"/>
-      <c r="G168" s="40" t="s">
+      <c r="H168" s="57"/>
+      <c r="I168" s="34" t="s">
         <v>434</v>
       </c>
-      <c r="H168" s="40"/>
-      <c r="I168" s="34" t="s">
+      <c r="J168" s="57" t="s">
         <v>435</v>
       </c>
-      <c r="J168" s="40" t="s">
+      <c r="K168" s="57"/>
+      <c r="L168" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="K168" s="40"/>
-      <c r="L168" s="40" t="s">
-        <v>437</v>
-      </c>
-      <c r="M168" s="40"/>
+      <c r="M168" s="57"/>
       <c r="N168" s="34" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O168" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P168" s="35"/>
+      <c r="P168" s="39"/>
     </row>
     <row r="169" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="35">
+      <c r="A169" s="39">
         <v>3</v>
       </c>
-      <c r="B169" s="35">
+      <c r="B169" s="39">
         <v>5</v>
       </c>
-      <c r="C169" s="35"/>
+      <c r="C169" s="39"/>
       <c r="D169" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E169" s="40" t="s">
+      <c r="E169" s="57" t="s">
+        <v>595</v>
+      </c>
+      <c r="F169" s="57"/>
+      <c r="G169" s="57" t="s">
         <v>596</v>
       </c>
-      <c r="F169" s="40"/>
-      <c r="G169" s="40" t="s">
+      <c r="H169" s="57"/>
+      <c r="I169" s="34" t="s">
         <v>597</v>
       </c>
-      <c r="H169" s="40"/>
-      <c r="I169" s="34" t="s">
+      <c r="J169" s="57" t="s">
         <v>598</v>
       </c>
-      <c r="J169" s="40" t="s">
+      <c r="K169" s="57"/>
+      <c r="L169" s="57" t="s">
         <v>599</v>
       </c>
-      <c r="K169" s="40"/>
-      <c r="L169" s="40" t="s">
+      <c r="M169" s="57"/>
+      <c r="N169" s="34" t="s">
         <v>600</v>
-      </c>
-      <c r="M169" s="40"/>
-      <c r="N169" s="34" t="s">
-        <v>601</v>
       </c>
       <c r="O169" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P169" s="35"/>
+      <c r="P169" s="39"/>
     </row>
     <row r="170" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="35"/>
-      <c r="B170" s="35">
+      <c r="A170" s="39"/>
+      <c r="B170" s="39">
         <v>10</v>
       </c>
-      <c r="C170" s="35"/>
+      <c r="C170" s="39"/>
       <c r="D170" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E170" s="40" t="s">
+      <c r="E170" s="57" t="s">
+        <v>437</v>
+      </c>
+      <c r="F170" s="57"/>
+      <c r="G170" s="57" t="s">
         <v>438</v>
       </c>
-      <c r="F170" s="40"/>
-      <c r="G170" s="40" t="s">
+      <c r="H170" s="57"/>
+      <c r="I170" s="34" t="s">
         <v>439</v>
       </c>
-      <c r="H170" s="40"/>
-      <c r="I170" s="34" t="s">
+      <c r="J170" s="57" t="s">
         <v>440</v>
       </c>
-      <c r="J170" s="40" t="s">
+      <c r="K170" s="57"/>
+      <c r="L170" s="57" t="s">
         <v>441</v>
       </c>
-      <c r="K170" s="40"/>
-      <c r="L170" s="40" t="s">
+      <c r="M170" s="57"/>
+      <c r="N170" s="34" t="s">
         <v>442</v>
-      </c>
-      <c r="M170" s="40"/>
-      <c r="N170" s="34" t="s">
-        <v>443</v>
       </c>
       <c r="O170" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P170" s="35"/>
+      <c r="P170" s="39"/>
     </row>
     <row r="171" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="35"/>
-      <c r="B171" s="35">
+      <c r="A171" s="39"/>
+      <c r="B171" s="39">
         <v>20</v>
       </c>
-      <c r="C171" s="35"/>
+      <c r="C171" s="39"/>
       <c r="D171" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E171" s="40" t="s">
+      <c r="E171" s="57" t="s">
+        <v>443</v>
+      </c>
+      <c r="F171" s="57"/>
+      <c r="G171" s="57" t="s">
         <v>444</v>
       </c>
-      <c r="F171" s="40"/>
-      <c r="G171" s="40" t="s">
+      <c r="H171" s="57"/>
+      <c r="I171" s="34" t="s">
         <v>445</v>
       </c>
-      <c r="H171" s="40"/>
-      <c r="I171" s="34" t="s">
+      <c r="J171" s="57" t="s">
         <v>446</v>
       </c>
-      <c r="J171" s="40" t="s">
+      <c r="K171" s="57"/>
+      <c r="L171" s="57" t="s">
         <v>447</v>
       </c>
-      <c r="K171" s="40"/>
-      <c r="L171" s="40" t="s">
+      <c r="M171" s="57"/>
+      <c r="N171" s="34" t="s">
         <v>448</v>
-      </c>
-      <c r="M171" s="40"/>
-      <c r="N171" s="34" t="s">
-        <v>449</v>
       </c>
       <c r="O171" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P171" s="35"/>
+      <c r="P171" s="39"/>
     </row>
     <row r="172" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="35"/>
-      <c r="B172" s="35">
+      <c r="A172" s="39"/>
+      <c r="B172" s="39">
         <v>50</v>
       </c>
-      <c r="C172" s="35"/>
+      <c r="C172" s="39"/>
       <c r="D172" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E172" s="40" t="s">
+      <c r="E172" s="57" t="s">
+        <v>449</v>
+      </c>
+      <c r="F172" s="57"/>
+      <c r="G172" s="57" t="s">
         <v>450</v>
       </c>
-      <c r="F172" s="40"/>
-      <c r="G172" s="40" t="s">
+      <c r="H172" s="57"/>
+      <c r="I172" s="34" t="s">
         <v>451</v>
       </c>
-      <c r="H172" s="40"/>
-      <c r="I172" s="34" t="s">
+      <c r="J172" s="57" t="s">
         <v>452</v>
       </c>
-      <c r="J172" s="40" t="s">
+      <c r="K172" s="57"/>
+      <c r="L172" s="57" t="s">
         <v>453</v>
       </c>
-      <c r="K172" s="40"/>
-      <c r="L172" s="40" t="s">
+      <c r="M172" s="57"/>
+      <c r="N172" s="34" t="s">
         <v>454</v>
-      </c>
-      <c r="M172" s="40"/>
-      <c r="N172" s="34" t="s">
-        <v>455</v>
       </c>
       <c r="O172" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P172" s="35"/>
+      <c r="P172" s="39"/>
     </row>
     <row r="173" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="35"/>
-      <c r="B173" s="35">
+      <c r="A173" s="39"/>
+      <c r="B173" s="39">
         <v>100</v>
       </c>
-      <c r="C173" s="35"/>
+      <c r="C173" s="39"/>
       <c r="D173" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E173" s="40" t="s">
+      <c r="E173" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="F173" s="57"/>
+      <c r="G173" s="57" t="s">
         <v>456</v>
       </c>
-      <c r="F173" s="40"/>
-      <c r="G173" s="40" t="s">
+      <c r="H173" s="57"/>
+      <c r="I173" s="34" t="s">
         <v>457</v>
       </c>
-      <c r="H173" s="40"/>
-      <c r="I173" s="34" t="s">
+      <c r="J173" s="57" t="s">
         <v>458</v>
       </c>
-      <c r="J173" s="40" t="s">
+      <c r="K173" s="57"/>
+      <c r="L173" s="57" t="s">
         <v>459</v>
       </c>
-      <c r="K173" s="40"/>
-      <c r="L173" s="40" t="s">
+      <c r="M173" s="57"/>
+      <c r="N173" s="34" t="s">
         <v>460</v>
-      </c>
-      <c r="M173" s="40"/>
-      <c r="N173" s="34" t="s">
-        <v>461</v>
       </c>
       <c r="O173" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P173" s="35"/>
+      <c r="P173" s="39"/>
     </row>
     <row r="174" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="35"/>
-      <c r="B174" s="35">
+      <c r="A174" s="39"/>
+      <c r="B174" s="39">
         <v>200</v>
       </c>
-      <c r="C174" s="35"/>
+      <c r="C174" s="39"/>
       <c r="D174" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E174" s="40" t="s">
+      <c r="E174" s="57" t="s">
+        <v>461</v>
+      </c>
+      <c r="F174" s="57"/>
+      <c r="G174" s="57" t="s">
         <v>462</v>
       </c>
-      <c r="F174" s="40"/>
-      <c r="G174" s="40" t="s">
+      <c r="H174" s="57"/>
+      <c r="I174" s="34" t="s">
         <v>463</v>
       </c>
-      <c r="H174" s="40"/>
-      <c r="I174" s="34" t="s">
+      <c r="J174" s="57" t="s">
         <v>464</v>
       </c>
-      <c r="J174" s="40" t="s">
+      <c r="K174" s="57"/>
+      <c r="L174" s="57" t="s">
         <v>465</v>
       </c>
-      <c r="K174" s="40"/>
-      <c r="L174" s="40" t="s">
+      <c r="M174" s="57"/>
+      <c r="N174" s="34" t="s">
         <v>466</v>
-      </c>
-      <c r="M174" s="40"/>
-      <c r="N174" s="34" t="s">
-        <v>467</v>
       </c>
       <c r="O174" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P174" s="35"/>
+      <c r="P174" s="39"/>
     </row>
     <row r="175" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="35"/>
-      <c r="B175" s="35">
+      <c r="A175" s="39"/>
+      <c r="B175" s="39">
         <v>500</v>
       </c>
-      <c r="C175" s="35"/>
+      <c r="C175" s="39"/>
       <c r="D175" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E175" s="40" t="s">
+      <c r="E175" s="57" t="s">
+        <v>467</v>
+      </c>
+      <c r="F175" s="57"/>
+      <c r="G175" s="57" t="s">
         <v>468</v>
       </c>
-      <c r="F175" s="40"/>
-      <c r="G175" s="40" t="s">
+      <c r="H175" s="57"/>
+      <c r="I175" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="H175" s="40"/>
-      <c r="I175" s="34" t="s">
+      <c r="J175" s="57" t="s">
         <v>470</v>
       </c>
-      <c r="J175" s="40" t="s">
+      <c r="K175" s="57"/>
+      <c r="L175" s="57" t="s">
         <v>471</v>
       </c>
-      <c r="K175" s="40"/>
-      <c r="L175" s="40" t="s">
+      <c r="M175" s="57"/>
+      <c r="N175" s="34" t="s">
         <v>472</v>
-      </c>
-      <c r="M175" s="40"/>
-      <c r="N175" s="34" t="s">
-        <v>473</v>
       </c>
       <c r="O175" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P175" s="35"/>
+      <c r="P175" s="39"/>
     </row>
     <row r="176" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="35"/>
-      <c r="B176" s="35">
+      <c r="A176" s="39"/>
+      <c r="B176" s="39">
         <v>1000</v>
       </c>
-      <c r="C176" s="35"/>
+      <c r="C176" s="39"/>
       <c r="D176" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E176" s="40" t="s">
+      <c r="E176" s="57" t="s">
+        <v>473</v>
+      </c>
+      <c r="F176" s="57"/>
+      <c r="G176" s="57" t="s">
         <v>474</v>
       </c>
-      <c r="F176" s="40"/>
-      <c r="G176" s="40" t="s">
+      <c r="H176" s="57"/>
+      <c r="I176" s="34" t="s">
         <v>475</v>
       </c>
-      <c r="H176" s="40"/>
-      <c r="I176" s="34" t="s">
+      <c r="J176" s="57" t="s">
         <v>476</v>
       </c>
-      <c r="J176" s="40" t="s">
+      <c r="K176" s="57"/>
+      <c r="L176" s="57" t="s">
         <v>477</v>
       </c>
-      <c r="K176" s="40"/>
-      <c r="L176" s="40" t="s">
+      <c r="M176" s="57"/>
+      <c r="N176" s="34" t="s">
         <v>478</v>
-      </c>
-      <c r="M176" s="40"/>
-      <c r="N176" s="34" t="s">
-        <v>479</v>
       </c>
       <c r="O176" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P176" s="35"/>
+      <c r="P176" s="39"/>
     </row>
     <row r="177" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="35">
+      <c r="A177" s="39">
         <v>4</v>
       </c>
-      <c r="B177" s="35">
+      <c r="B177" s="39">
         <v>5</v>
       </c>
-      <c r="C177" s="35"/>
+      <c r="C177" s="39"/>
       <c r="D177" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E177" s="40" t="s">
+      <c r="E177" s="57" t="s">
+        <v>601</v>
+      </c>
+      <c r="F177" s="57"/>
+      <c r="G177" s="57" t="s">
         <v>602</v>
       </c>
-      <c r="F177" s="40"/>
-      <c r="G177" s="40" t="s">
+      <c r="H177" s="57"/>
+      <c r="I177" s="34" t="s">
         <v>603</v>
       </c>
-      <c r="H177" s="40"/>
-      <c r="I177" s="34" t="s">
+      <c r="J177" s="57" t="s">
         <v>604</v>
       </c>
-      <c r="J177" s="40" t="s">
+      <c r="K177" s="57"/>
+      <c r="L177" s="57" t="s">
         <v>605</v>
       </c>
-      <c r="K177" s="40"/>
-      <c r="L177" s="40" t="s">
+      <c r="M177" s="57"/>
+      <c r="N177" s="34" t="s">
         <v>606</v>
-      </c>
-      <c r="M177" s="40"/>
-      <c r="N177" s="34" t="s">
-        <v>607</v>
       </c>
       <c r="O177" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P177" s="35"/>
+      <c r="P177" s="39"/>
     </row>
     <row r="178" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="35"/>
-      <c r="B178" s="35">
+      <c r="A178" s="39"/>
+      <c r="B178" s="39">
         <v>10</v>
       </c>
-      <c r="C178" s="35"/>
+      <c r="C178" s="39"/>
       <c r="D178" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E178" s="40" t="s">
+      <c r="E178" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="F178" s="57"/>
+      <c r="G178" s="57" t="s">
         <v>480</v>
       </c>
-      <c r="F178" s="40"/>
-      <c r="G178" s="40" t="s">
+      <c r="H178" s="57"/>
+      <c r="I178" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="H178" s="40"/>
-      <c r="I178" s="34" t="s">
+      <c r="J178" s="57" t="s">
         <v>482</v>
       </c>
-      <c r="J178" s="40" t="s">
+      <c r="K178" s="57"/>
+      <c r="L178" s="57" t="s">
         <v>483</v>
       </c>
-      <c r="K178" s="40"/>
-      <c r="L178" s="40" t="s">
+      <c r="M178" s="57"/>
+      <c r="N178" s="34" t="s">
         <v>484</v>
-      </c>
-      <c r="M178" s="40"/>
-      <c r="N178" s="34" t="s">
-        <v>485</v>
       </c>
       <c r="O178" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P178" s="35"/>
+      <c r="P178" s="39"/>
     </row>
     <row r="179" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="35"/>
-      <c r="B179" s="35">
+      <c r="A179" s="39"/>
+      <c r="B179" s="39">
         <v>20</v>
       </c>
-      <c r="C179" s="35"/>
+      <c r="C179" s="39"/>
       <c r="D179" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E179" s="40" t="s">
+      <c r="E179" s="57" t="s">
+        <v>485</v>
+      </c>
+      <c r="F179" s="57"/>
+      <c r="G179" s="57" t="s">
         <v>486</v>
       </c>
-      <c r="F179" s="40"/>
-      <c r="G179" s="40" t="s">
+      <c r="H179" s="57"/>
+      <c r="I179" s="34" t="s">
         <v>487</v>
       </c>
-      <c r="H179" s="40"/>
-      <c r="I179" s="34" t="s">
+      <c r="J179" s="57" t="s">
         <v>488</v>
       </c>
-      <c r="J179" s="40" t="s">
+      <c r="K179" s="57"/>
+      <c r="L179" s="57" t="s">
         <v>489</v>
       </c>
-      <c r="K179" s="40"/>
-      <c r="L179" s="40" t="s">
+      <c r="M179" s="57"/>
+      <c r="N179" s="34" t="s">
         <v>490</v>
-      </c>
-      <c r="M179" s="40"/>
-      <c r="N179" s="34" t="s">
-        <v>491</v>
       </c>
       <c r="O179" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P179" s="35"/>
+      <c r="P179" s="39"/>
     </row>
     <row r="180" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="35"/>
-      <c r="B180" s="35">
+      <c r="A180" s="39"/>
+      <c r="B180" s="39">
         <v>50</v>
       </c>
-      <c r="C180" s="35"/>
+      <c r="C180" s="39"/>
       <c r="D180" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E180" s="40" t="s">
+      <c r="E180" s="57" t="s">
+        <v>491</v>
+      </c>
+      <c r="F180" s="57"/>
+      <c r="G180" s="57" t="s">
         <v>492</v>
       </c>
-      <c r="F180" s="40"/>
-      <c r="G180" s="40" t="s">
+      <c r="H180" s="57"/>
+      <c r="I180" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="H180" s="40"/>
-      <c r="I180" s="34" t="s">
+      <c r="J180" s="57" t="s">
         <v>494</v>
       </c>
-      <c r="J180" s="40" t="s">
+      <c r="K180" s="57"/>
+      <c r="L180" s="57" t="s">
         <v>495</v>
       </c>
-      <c r="K180" s="40"/>
-      <c r="L180" s="40" t="s">
+      <c r="M180" s="57"/>
+      <c r="N180" s="34" t="s">
         <v>496</v>
-      </c>
-      <c r="M180" s="40"/>
-      <c r="N180" s="34" t="s">
-        <v>497</v>
       </c>
       <c r="O180" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P180" s="35"/>
+      <c r="P180" s="39"/>
     </row>
     <row r="181" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="35"/>
-      <c r="B181" s="35">
+      <c r="A181" s="39"/>
+      <c r="B181" s="39">
         <v>100</v>
       </c>
-      <c r="C181" s="35"/>
+      <c r="C181" s="39"/>
       <c r="D181" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E181" s="40" t="s">
+      <c r="E181" s="57" t="s">
+        <v>497</v>
+      </c>
+      <c r="F181" s="57"/>
+      <c r="G181" s="57" t="s">
         <v>498</v>
       </c>
-      <c r="F181" s="40"/>
-      <c r="G181" s="40" t="s">
+      <c r="H181" s="57"/>
+      <c r="I181" s="34" t="s">
         <v>499</v>
       </c>
-      <c r="H181" s="40"/>
-      <c r="I181" s="34" t="s">
+      <c r="J181" s="57" t="s">
         <v>500</v>
       </c>
-      <c r="J181" s="40" t="s">
+      <c r="K181" s="57"/>
+      <c r="L181" s="57" t="s">
         <v>501</v>
       </c>
-      <c r="K181" s="40"/>
-      <c r="L181" s="40" t="s">
+      <c r="M181" s="57"/>
+      <c r="N181" s="34" t="s">
         <v>502</v>
-      </c>
-      <c r="M181" s="40"/>
-      <c r="N181" s="34" t="s">
-        <v>503</v>
       </c>
       <c r="O181" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P181" s="35"/>
+      <c r="P181" s="39"/>
     </row>
     <row r="182" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="35"/>
-      <c r="B182" s="35">
+      <c r="A182" s="39"/>
+      <c r="B182" s="39">
         <v>200</v>
       </c>
-      <c r="C182" s="35"/>
+      <c r="C182" s="39"/>
       <c r="D182" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E182" s="40" t="s">
+      <c r="E182" s="57" t="s">
+        <v>503</v>
+      </c>
+      <c r="F182" s="57"/>
+      <c r="G182" s="57" t="s">
         <v>504</v>
       </c>
-      <c r="F182" s="40"/>
-      <c r="G182" s="40" t="s">
+      <c r="H182" s="57"/>
+      <c r="I182" s="34" t="s">
         <v>505</v>
       </c>
-      <c r="H182" s="40"/>
-      <c r="I182" s="34" t="s">
+      <c r="J182" s="57" t="s">
         <v>506</v>
       </c>
-      <c r="J182" s="40" t="s">
+      <c r="K182" s="57"/>
+      <c r="L182" s="57" t="s">
         <v>507</v>
       </c>
-      <c r="K182" s="40"/>
-      <c r="L182" s="40" t="s">
+      <c r="M182" s="57"/>
+      <c r="N182" s="34" t="s">
         <v>508</v>
-      </c>
-      <c r="M182" s="40"/>
-      <c r="N182" s="34" t="s">
-        <v>509</v>
       </c>
       <c r="O182" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P182" s="35"/>
+      <c r="P182" s="39"/>
     </row>
     <row r="183" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="35"/>
-      <c r="B183" s="35">
+      <c r="A183" s="39"/>
+      <c r="B183" s="39">
         <v>500</v>
       </c>
-      <c r="C183" s="35"/>
+      <c r="C183" s="39"/>
       <c r="D183" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E183" s="40" t="s">
+      <c r="E183" s="57" t="s">
+        <v>509</v>
+      </c>
+      <c r="F183" s="57"/>
+      <c r="G183" s="57" t="s">
         <v>510</v>
       </c>
-      <c r="F183" s="40"/>
-      <c r="G183" s="40" t="s">
+      <c r="H183" s="57"/>
+      <c r="I183" s="34" t="s">
         <v>511</v>
       </c>
-      <c r="H183" s="40"/>
-      <c r="I183" s="34" t="s">
+      <c r="J183" s="57" t="s">
         <v>512</v>
       </c>
-      <c r="J183" s="40" t="s">
+      <c r="K183" s="57"/>
+      <c r="L183" s="57" t="s">
         <v>513</v>
       </c>
-      <c r="K183" s="40"/>
-      <c r="L183" s="40" t="s">
+      <c r="M183" s="57"/>
+      <c r="N183" s="34" t="s">
         <v>514</v>
-      </c>
-      <c r="M183" s="40"/>
-      <c r="N183" s="34" t="s">
-        <v>515</v>
       </c>
       <c r="O183" s="28" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P183" s="35"/>
+      <c r="P183" s="39"/>
     </row>
     <row r="184" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="38" t="s">
+      <c r="A184" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B184" s="38" t="s">
+      <c r="B184" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C184" s="38"/>
-      <c r="D184" s="38" t="s">
+      <c r="C184" s="47"/>
+      <c r="D184" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E184" s="38" t="s">
+      <c r="E184" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="F184" s="38"/>
-      <c r="G184" s="38" t="s">
+      <c r="F184" s="47"/>
+      <c r="G184" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="H184" s="38"/>
-      <c r="I184" s="38" t="s">
+      <c r="H184" s="47"/>
+      <c r="I184" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="J184" s="38" t="s">
+      <c r="J184" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="K184" s="38"/>
-      <c r="L184" s="38" t="s">
+      <c r="K184" s="47"/>
+      <c r="L184" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="M184" s="38"/>
-      <c r="N184" s="38" t="s">
+      <c r="M184" s="47"/>
+      <c r="N184" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="O184" s="38" t="s">
+      <c r="O184" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="P184" s="41" t="s">
+      <c r="P184" s="65" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="185" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="38"/>
-      <c r="B185" s="38"/>
-      <c r="C185" s="38"/>
-      <c r="D185" s="38"/>
-      <c r="E185" s="38"/>
-      <c r="F185" s="38"/>
-      <c r="G185" s="38"/>
-      <c r="H185" s="38"/>
-      <c r="I185" s="38"/>
-      <c r="J185" s="38"/>
-      <c r="K185" s="38"/>
-      <c r="L185" s="38"/>
-      <c r="M185" s="38"/>
-      <c r="N185" s="38"/>
-      <c r="O185" s="38"/>
-      <c r="P185" s="38"/>
+      <c r="A185" s="47"/>
+      <c r="B185" s="47"/>
+      <c r="C185" s="47"/>
+      <c r="D185" s="47"/>
+      <c r="E185" s="47"/>
+      <c r="F185" s="47"/>
+      <c r="G185" s="47"/>
+      <c r="H185" s="47"/>
+      <c r="I185" s="47"/>
+      <c r="J185" s="47"/>
+      <c r="K185" s="47"/>
+      <c r="L185" s="47"/>
+      <c r="M185" s="47"/>
+      <c r="N185" s="47"/>
+      <c r="O185" s="47"/>
+      <c r="P185" s="47"/>
     </row>
     <row r="186" spans="1:16" s="1" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="38"/>
-      <c r="B186" s="38"/>
-      <c r="C186" s="38"/>
-      <c r="D186" s="38"/>
-      <c r="E186" s="38"/>
-      <c r="F186" s="38"/>
-      <c r="G186" s="38"/>
-      <c r="H186" s="38"/>
-      <c r="I186" s="38"/>
-      <c r="J186" s="38"/>
-      <c r="K186" s="38"/>
-      <c r="L186" s="38"/>
-      <c r="M186" s="38"/>
-      <c r="N186" s="38"/>
-      <c r="O186" s="38"/>
-      <c r="P186" s="38"/>
+      <c r="A186" s="47"/>
+      <c r="B186" s="47"/>
+      <c r="C186" s="47"/>
+      <c r="D186" s="47"/>
+      <c r="E186" s="47"/>
+      <c r="F186" s="47"/>
+      <c r="G186" s="47"/>
+      <c r="H186" s="47"/>
+      <c r="I186" s="47"/>
+      <c r="J186" s="47"/>
+      <c r="K186" s="47"/>
+      <c r="L186" s="47"/>
+      <c r="M186" s="47"/>
+      <c r="N186" s="47"/>
+      <c r="O186" s="47"/>
+      <c r="P186" s="47"/>
     </row>
     <row r="187" spans="1:16" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="17">
         <v>4</v>
       </c>
-      <c r="B187" s="35">
+      <c r="B187" s="39">
         <v>1000</v>
       </c>
-      <c r="C187" s="35"/>
+      <c r="C187" s="39"/>
       <c r="D187" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E187" s="40" t="s">
+      <c r="E187" s="57" t="s">
+        <v>515</v>
+      </c>
+      <c r="F187" s="57"/>
+      <c r="G187" s="57" t="s">
         <v>516</v>
       </c>
-      <c r="F187" s="40"/>
-      <c r="G187" s="40" t="s">
+      <c r="H187" s="57"/>
+      <c r="I187" s="34" t="s">
         <v>517</v>
       </c>
-      <c r="H187" s="40"/>
-      <c r="I187" s="34" t="s">
+      <c r="J187" s="57" t="s">
         <v>518</v>
       </c>
-      <c r="J187" s="40" t="s">
+      <c r="K187" s="57"/>
+      <c r="L187" s="57" t="s">
         <v>519</v>
       </c>
-      <c r="K187" s="40"/>
-      <c r="L187" s="40" t="s">
+      <c r="M187" s="57"/>
+      <c r="N187" s="34" t="s">
         <v>520</v>
-      </c>
-      <c r="M187" s="40"/>
-      <c r="N187" s="34" t="s">
-        <v>521</v>
       </c>
       <c r="O187" s="26" t="e">
         <f>IF(ABS(((J187-N187)/(E187-I187)-1)*100)&gt;ABS(((L187-N187)/(G187-I187)-1)*100),((J187-N187)/(E187-I187)-1)*100,((L187-N187)/(G187-I187)-1)*100)</f>
@@ -9859,309 +9850,309 @@
       <c r="P190" s="15"/>
     </row>
     <row r="191" spans="1:16" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="38" t="s">
+      <c r="A191" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B191" s="38"/>
-      <c r="C191" s="38"/>
-      <c r="D191" s="38" t="s">
+      <c r="B191" s="47"/>
+      <c r="C191" s="47"/>
+      <c r="D191" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="E191" s="38"/>
-      <c r="F191" s="35" t="s">
+      <c r="E191" s="47"/>
+      <c r="F191" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="G191" s="35"/>
-      <c r="H191" s="35"/>
-      <c r="I191" s="35"/>
-      <c r="J191" s="35"/>
-      <c r="K191" s="35"/>
-      <c r="L191" s="35"/>
-      <c r="M191" s="35"/>
+      <c r="G191" s="39"/>
+      <c r="H191" s="39"/>
+      <c r="I191" s="39"/>
+      <c r="J191" s="39"/>
+      <c r="K191" s="39"/>
+      <c r="L191" s="39"/>
+      <c r="M191" s="39"/>
       <c r="N191" s="15"/>
       <c r="O191" s="15"/>
       <c r="P191" s="15"/>
     </row>
     <row r="192" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="38"/>
-      <c r="B192" s="38"/>
-      <c r="C192" s="38"/>
-      <c r="D192" s="38"/>
-      <c r="E192" s="38"/>
-      <c r="F192" s="35"/>
-      <c r="G192" s="35"/>
-      <c r="H192" s="35"/>
-      <c r="I192" s="35"/>
-      <c r="J192" s="35"/>
-      <c r="K192" s="35"/>
-      <c r="L192" s="35"/>
-      <c r="M192" s="35"/>
+      <c r="A192" s="47"/>
+      <c r="B192" s="47"/>
+      <c r="C192" s="47"/>
+      <c r="D192" s="47"/>
+      <c r="E192" s="47"/>
+      <c r="F192" s="39"/>
+      <c r="G192" s="39"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="39"/>
+      <c r="J192" s="39"/>
+      <c r="K192" s="39"/>
+      <c r="L192" s="39"/>
+      <c r="M192" s="39"/>
       <c r="N192" s="15"/>
       <c r="O192" s="15"/>
       <c r="P192" s="15"/>
     </row>
     <row r="193" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="38"/>
-      <c r="B193" s="38"/>
-      <c r="C193" s="38"/>
-      <c r="D193" s="38"/>
-      <c r="E193" s="38"/>
-      <c r="F193" s="35" t="s">
+      <c r="A193" s="47"/>
+      <c r="B193" s="47"/>
+      <c r="C193" s="47"/>
+      <c r="D193" s="47"/>
+      <c r="E193" s="47"/>
+      <c r="F193" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="G193" s="35"/>
-      <c r="H193" s="35" t="s">
+      <c r="G193" s="39"/>
+      <c r="H193" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="I193" s="35"/>
-      <c r="J193" s="35" t="s">
+      <c r="I193" s="39"/>
+      <c r="J193" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="K193" s="35"/>
-      <c r="L193" s="35" t="s">
+      <c r="K193" s="39"/>
+      <c r="L193" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="M193" s="35"/>
+      <c r="M193" s="39"/>
       <c r="N193" s="15"/>
       <c r="O193" s="15"/>
       <c r="P193" s="15"/>
     </row>
     <row r="194" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A194" s="35">
+      <c r="A194" s="39">
         <v>5</v>
       </c>
-      <c r="B194" s="35"/>
-      <c r="C194" s="35"/>
-      <c r="D194" s="37" t="s">
+      <c r="B194" s="39"/>
+      <c r="C194" s="39"/>
+      <c r="D194" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="E194" s="37"/>
-      <c r="F194" s="36" t="s">
+      <c r="E194" s="66"/>
+      <c r="F194" s="59" t="s">
+        <v>572</v>
+      </c>
+      <c r="G194" s="59"/>
+      <c r="H194" s="59" t="s">
         <v>573</v>
       </c>
-      <c r="G194" s="36"/>
-      <c r="H194" s="36" t="s">
+      <c r="I194" s="59"/>
+      <c r="J194" s="59" t="s">
         <v>574</v>
       </c>
-      <c r="I194" s="36"/>
-      <c r="J194" s="36" t="s">
+      <c r="K194" s="59"/>
+      <c r="L194" s="59" t="s">
         <v>575</v>
       </c>
-      <c r="K194" s="36"/>
-      <c r="L194" s="36" t="s">
-        <v>576</v>
-      </c>
-      <c r="M194" s="36"/>
+      <c r="M194" s="59"/>
       <c r="N194" s="15"/>
       <c r="O194" s="15"/>
       <c r="P194" s="15"/>
     </row>
     <row r="195" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A195" s="35">
+      <c r="A195" s="39">
         <v>10</v>
       </c>
-      <c r="B195" s="35"/>
-      <c r="C195" s="35"/>
-      <c r="D195" s="37" t="s">
+      <c r="B195" s="39"/>
+      <c r="C195" s="39"/>
+      <c r="D195" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E195" s="37"/>
-      <c r="F195" s="36" t="s">
+      <c r="E195" s="66"/>
+      <c r="F195" s="59" t="s">
+        <v>521</v>
+      </c>
+      <c r="G195" s="59"/>
+      <c r="H195" s="59" t="s">
         <v>522</v>
       </c>
-      <c r="G195" s="36"/>
-      <c r="H195" s="36" t="s">
+      <c r="I195" s="59"/>
+      <c r="J195" s="59" t="s">
         <v>523</v>
       </c>
-      <c r="I195" s="36"/>
-      <c r="J195" s="36" t="s">
+      <c r="K195" s="59"/>
+      <c r="L195" s="59" t="s">
         <v>524</v>
       </c>
-      <c r="K195" s="36"/>
-      <c r="L195" s="36" t="s">
-        <v>525</v>
-      </c>
-      <c r="M195" s="36"/>
+      <c r="M195" s="59"/>
       <c r="N195" s="15"/>
       <c r="O195" s="15"/>
       <c r="P195" s="15"/>
     </row>
     <row r="196" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A196" s="35">
+      <c r="A196" s="39">
         <v>20</v>
       </c>
-      <c r="B196" s="35"/>
-      <c r="C196" s="35"/>
-      <c r="D196" s="37" t="s">
+      <c r="B196" s="39"/>
+      <c r="C196" s="39"/>
+      <c r="D196" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="E196" s="37"/>
-      <c r="F196" s="36" t="s">
+      <c r="E196" s="66"/>
+      <c r="F196" s="59" t="s">
+        <v>525</v>
+      </c>
+      <c r="G196" s="59"/>
+      <c r="H196" s="59" t="s">
         <v>526</v>
       </c>
-      <c r="G196" s="36"/>
-      <c r="H196" s="36" t="s">
+      <c r="I196" s="59"/>
+      <c r="J196" s="59" t="s">
         <v>527</v>
       </c>
-      <c r="I196" s="36"/>
-      <c r="J196" s="36" t="s">
+      <c r="K196" s="59"/>
+      <c r="L196" s="59" t="s">
         <v>528</v>
       </c>
-      <c r="K196" s="36"/>
-      <c r="L196" s="36" t="s">
-        <v>529</v>
-      </c>
-      <c r="M196" s="36"/>
+      <c r="M196" s="59"/>
       <c r="N196" s="15"/>
       <c r="O196" s="15"/>
       <c r="P196" s="15"/>
     </row>
     <row r="197" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A197" s="35">
+      <c r="A197" s="39">
         <v>50</v>
       </c>
-      <c r="B197" s="35"/>
-      <c r="C197" s="35"/>
-      <c r="D197" s="37" t="s">
+      <c r="B197" s="39"/>
+      <c r="C197" s="39"/>
+      <c r="D197" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="E197" s="37"/>
-      <c r="F197" s="36" t="s">
+      <c r="E197" s="66"/>
+      <c r="F197" s="59" t="s">
+        <v>529</v>
+      </c>
+      <c r="G197" s="59"/>
+      <c r="H197" s="59" t="s">
         <v>530</v>
       </c>
-      <c r="G197" s="36"/>
-      <c r="H197" s="36" t="s">
+      <c r="I197" s="59"/>
+      <c r="J197" s="59" t="s">
         <v>531</v>
       </c>
-      <c r="I197" s="36"/>
-      <c r="J197" s="36" t="s">
+      <c r="K197" s="59"/>
+      <c r="L197" s="59" t="s">
         <v>532</v>
       </c>
-      <c r="K197" s="36"/>
-      <c r="L197" s="36" t="s">
-        <v>533</v>
-      </c>
-      <c r="M197" s="36"/>
+      <c r="M197" s="59"/>
       <c r="N197" s="15"/>
       <c r="O197" s="15"/>
       <c r="P197" s="15"/>
     </row>
     <row r="198" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A198" s="35">
+      <c r="A198" s="39">
         <v>100</v>
       </c>
-      <c r="B198" s="35"/>
-      <c r="C198" s="35"/>
-      <c r="D198" s="37" t="s">
+      <c r="B198" s="39"/>
+      <c r="C198" s="39"/>
+      <c r="D198" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="E198" s="37"/>
-      <c r="F198" s="36" t="s">
+      <c r="E198" s="66"/>
+      <c r="F198" s="59" t="s">
+        <v>533</v>
+      </c>
+      <c r="G198" s="59"/>
+      <c r="H198" s="59" t="s">
         <v>534</v>
       </c>
-      <c r="G198" s="36"/>
-      <c r="H198" s="36" t="s">
+      <c r="I198" s="59"/>
+      <c r="J198" s="59" t="s">
         <v>535</v>
       </c>
-      <c r="I198" s="36"/>
-      <c r="J198" s="36" t="s">
+      <c r="K198" s="59"/>
+      <c r="L198" s="59" t="s">
         <v>536</v>
       </c>
-      <c r="K198" s="36"/>
-      <c r="L198" s="36" t="s">
-        <v>537</v>
-      </c>
-      <c r="M198" s="36"/>
+      <c r="M198" s="59"/>
       <c r="N198" s="15"/>
       <c r="O198" s="15"/>
       <c r="P198" s="15"/>
     </row>
     <row r="199" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A199" s="35">
+      <c r="A199" s="39">
         <v>200</v>
       </c>
-      <c r="B199" s="35"/>
-      <c r="C199" s="35"/>
-      <c r="D199" s="37" t="s">
+      <c r="B199" s="39"/>
+      <c r="C199" s="39"/>
+      <c r="D199" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="E199" s="37"/>
-      <c r="F199" s="36" t="s">
+      <c r="E199" s="66"/>
+      <c r="F199" s="59" t="s">
+        <v>537</v>
+      </c>
+      <c r="G199" s="59"/>
+      <c r="H199" s="59" t="s">
         <v>538</v>
       </c>
-      <c r="G199" s="36"/>
-      <c r="H199" s="36" t="s">
+      <c r="I199" s="59"/>
+      <c r="J199" s="59" t="s">
         <v>539</v>
       </c>
-      <c r="I199" s="36"/>
-      <c r="J199" s="36" t="s">
+      <c r="K199" s="59"/>
+      <c r="L199" s="59" t="s">
         <v>540</v>
       </c>
-      <c r="K199" s="36"/>
-      <c r="L199" s="36" t="s">
-        <v>541</v>
-      </c>
-      <c r="M199" s="36"/>
+      <c r="M199" s="59"/>
       <c r="N199" s="15"/>
       <c r="O199" s="15"/>
       <c r="P199" s="15"/>
     </row>
     <row r="200" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A200" s="35">
+      <c r="A200" s="39">
         <v>500</v>
       </c>
-      <c r="B200" s="35"/>
-      <c r="C200" s="35"/>
-      <c r="D200" s="37" t="s">
+      <c r="B200" s="39"/>
+      <c r="C200" s="39"/>
+      <c r="D200" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="E200" s="37"/>
-      <c r="F200" s="36" t="s">
+      <c r="E200" s="66"/>
+      <c r="F200" s="59" t="s">
+        <v>541</v>
+      </c>
+      <c r="G200" s="59"/>
+      <c r="H200" s="59" t="s">
         <v>542</v>
       </c>
-      <c r="G200" s="36"/>
-      <c r="H200" s="36" t="s">
+      <c r="I200" s="59"/>
+      <c r="J200" s="59" t="s">
         <v>543</v>
       </c>
-      <c r="I200" s="36"/>
-      <c r="J200" s="36" t="s">
+      <c r="K200" s="59"/>
+      <c r="L200" s="59" t="s">
         <v>544</v>
       </c>
-      <c r="K200" s="36"/>
-      <c r="L200" s="36" t="s">
-        <v>545</v>
-      </c>
-      <c r="M200" s="36"/>
+      <c r="M200" s="59"/>
       <c r="N200" s="15"/>
       <c r="O200" s="15"/>
       <c r="P200" s="15"/>
     </row>
     <row r="201" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="35">
+      <c r="A201" s="39">
         <v>1000</v>
       </c>
-      <c r="B201" s="35"/>
-      <c r="C201" s="35"/>
-      <c r="D201" s="37" t="s">
+      <c r="B201" s="39"/>
+      <c r="C201" s="39"/>
+      <c r="D201" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="E201" s="37"/>
-      <c r="F201" s="36" t="s">
+      <c r="E201" s="66"/>
+      <c r="F201" s="59" t="s">
+        <v>545</v>
+      </c>
+      <c r="G201" s="59"/>
+      <c r="H201" s="59" t="s">
         <v>546</v>
       </c>
-      <c r="G201" s="36"/>
-      <c r="H201" s="36" t="s">
+      <c r="I201" s="59"/>
+      <c r="J201" s="59" t="s">
         <v>547</v>
       </c>
-      <c r="I201" s="36"/>
-      <c r="J201" s="36" t="s">
+      <c r="K201" s="59"/>
+      <c r="L201" s="59" t="s">
         <v>548</v>
       </c>
-      <c r="K201" s="36"/>
-      <c r="L201" s="36" t="s">
-        <v>549</v>
-      </c>
-      <c r="M201" s="36"/>
+      <c r="M201" s="59"/>
       <c r="N201" s="15"/>
       <c r="O201" s="15"/>
       <c r="P201" s="15"/>
@@ -10186,7 +10177,7 @@
     </row>
     <row r="203" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A203" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -10279,29 +10270,29 @@
       <c r="P207" s="15"/>
     </row>
     <row r="208" spans="1:16" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="62" t="s">
-        <v>551</v>
-      </c>
-      <c r="B208" s="62"/>
+      <c r="A208" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="B208" s="35"/>
       <c r="C208" s="31"/>
       <c r="D208" s="32" t="s">
+        <v>551</v>
+      </c>
+      <c r="E208" s="36" t="s">
         <v>552</v>
       </c>
-      <c r="E208" s="63" t="s">
+      <c r="F208" s="37"/>
+      <c r="G208" s="33" t="s">
         <v>553</v>
       </c>
-      <c r="F208" s="64"/>
-      <c r="G208" s="33" t="s">
+      <c r="H208" s="35" t="s">
         <v>554</v>
       </c>
-      <c r="H208" s="62" t="s">
+      <c r="I208" s="35"/>
+      <c r="J208" s="38" t="s">
         <v>555</v>
       </c>
-      <c r="I208" s="62"/>
-      <c r="J208" s="65" t="s">
-        <v>556</v>
-      </c>
-      <c r="K208" s="65"/>
+      <c r="K208" s="38"/>
       <c r="L208" s="15"/>
       <c r="M208" s="15"/>
       <c r="N208" s="15"/>
@@ -10395,6 +10386,699 @@
     <row r="225" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="717">
+    <mergeCell ref="A201:C201"/>
+    <mergeCell ref="H201:I201"/>
+    <mergeCell ref="J201:K201"/>
+    <mergeCell ref="L201:M201"/>
+    <mergeCell ref="A199:C199"/>
+    <mergeCell ref="H199:I199"/>
+    <mergeCell ref="J199:K199"/>
+    <mergeCell ref="L199:M199"/>
+    <mergeCell ref="A200:C200"/>
+    <mergeCell ref="H200:I200"/>
+    <mergeCell ref="J200:K200"/>
+    <mergeCell ref="L200:M200"/>
+    <mergeCell ref="D199:E199"/>
+    <mergeCell ref="D200:E200"/>
+    <mergeCell ref="D201:E201"/>
+    <mergeCell ref="F201:G201"/>
+    <mergeCell ref="A191:C193"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="H197:I197"/>
+    <mergeCell ref="J197:K197"/>
+    <mergeCell ref="L197:M197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="H198:I198"/>
+    <mergeCell ref="J198:K198"/>
+    <mergeCell ref="L198:M198"/>
+    <mergeCell ref="H195:I195"/>
+    <mergeCell ref="J195:K195"/>
+    <mergeCell ref="L195:M195"/>
+    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="H196:I196"/>
+    <mergeCell ref="J196:K196"/>
+    <mergeCell ref="L196:M196"/>
+    <mergeCell ref="A195:C195"/>
+    <mergeCell ref="D196:E196"/>
+    <mergeCell ref="D197:E197"/>
+    <mergeCell ref="D198:E198"/>
+    <mergeCell ref="D191:E193"/>
+    <mergeCell ref="D194:E194"/>
+    <mergeCell ref="D195:E195"/>
+    <mergeCell ref="F191:M192"/>
+    <mergeCell ref="A16:P16"/>
+    <mergeCell ref="A169:A176"/>
+    <mergeCell ref="B184:C186"/>
+    <mergeCell ref="D184:D186"/>
+    <mergeCell ref="E184:F186"/>
+    <mergeCell ref="G184:H186"/>
+    <mergeCell ref="I184:I186"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="N184:N186"/>
+    <mergeCell ref="O150:O152"/>
+    <mergeCell ref="P150:P152"/>
+    <mergeCell ref="N150:N152"/>
+    <mergeCell ref="O184:O186"/>
+    <mergeCell ref="P184:P186"/>
+    <mergeCell ref="P153:P183"/>
+    <mergeCell ref="J182:K182"/>
+    <mergeCell ref="L182:M182"/>
+    <mergeCell ref="J183:K183"/>
+    <mergeCell ref="L183:M183"/>
+    <mergeCell ref="J176:K176"/>
+    <mergeCell ref="L176:M176"/>
+    <mergeCell ref="J177:K177"/>
+    <mergeCell ref="J187:K187"/>
+    <mergeCell ref="L187:M187"/>
+    <mergeCell ref="J184:K186"/>
+    <mergeCell ref="L184:M186"/>
+    <mergeCell ref="J179:K179"/>
+    <mergeCell ref="L179:M179"/>
+    <mergeCell ref="J180:K180"/>
+    <mergeCell ref="L180:M180"/>
+    <mergeCell ref="J181:K181"/>
+    <mergeCell ref="L181:M181"/>
+    <mergeCell ref="L177:M177"/>
+    <mergeCell ref="J178:K178"/>
+    <mergeCell ref="L178:M178"/>
+    <mergeCell ref="J174:K174"/>
+    <mergeCell ref="L174:M174"/>
+    <mergeCell ref="J175:K175"/>
+    <mergeCell ref="L175:M175"/>
+    <mergeCell ref="A177:A183"/>
+    <mergeCell ref="A184:A186"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="E174:F174"/>
+    <mergeCell ref="G174:H174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="G179:H179"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="G180:H180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="E181:F181"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="J171:K171"/>
+    <mergeCell ref="L171:M171"/>
+    <mergeCell ref="J172:K172"/>
+    <mergeCell ref="L172:M172"/>
+    <mergeCell ref="J173:K173"/>
+    <mergeCell ref="L173:M173"/>
+    <mergeCell ref="J168:K168"/>
+    <mergeCell ref="L168:M168"/>
+    <mergeCell ref="J169:K169"/>
+    <mergeCell ref="L169:M169"/>
+    <mergeCell ref="J170:K170"/>
+    <mergeCell ref="L170:M170"/>
+    <mergeCell ref="J165:K165"/>
+    <mergeCell ref="L165:M165"/>
+    <mergeCell ref="J166:K166"/>
+    <mergeCell ref="L166:M166"/>
+    <mergeCell ref="J167:K167"/>
+    <mergeCell ref="L167:M167"/>
+    <mergeCell ref="J162:K162"/>
+    <mergeCell ref="L162:M162"/>
+    <mergeCell ref="J163:K163"/>
+    <mergeCell ref="L163:M163"/>
+    <mergeCell ref="J164:K164"/>
+    <mergeCell ref="L164:M164"/>
+    <mergeCell ref="J159:K159"/>
+    <mergeCell ref="L159:M159"/>
+    <mergeCell ref="J160:K160"/>
+    <mergeCell ref="L160:M160"/>
+    <mergeCell ref="J161:K161"/>
+    <mergeCell ref="L161:M161"/>
+    <mergeCell ref="J156:K156"/>
+    <mergeCell ref="L156:M156"/>
+    <mergeCell ref="J157:K157"/>
+    <mergeCell ref="L157:M157"/>
+    <mergeCell ref="J158:K158"/>
+    <mergeCell ref="L158:M158"/>
+    <mergeCell ref="J153:K153"/>
+    <mergeCell ref="L153:M153"/>
+    <mergeCell ref="J154:K154"/>
+    <mergeCell ref="L154:M154"/>
+    <mergeCell ref="J155:K155"/>
+    <mergeCell ref="L155:M155"/>
+    <mergeCell ref="H111:H139"/>
+    <mergeCell ref="J150:K152"/>
+    <mergeCell ref="M74:N76"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="B74:C76"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="E74:F76"/>
+    <mergeCell ref="G74:H76"/>
+    <mergeCell ref="L150:M152"/>
+    <mergeCell ref="M98:N98"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="O74:O76"/>
+    <mergeCell ref="O77:O102"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="M94:N94"/>
+    <mergeCell ref="M97:N97"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="I74:J76"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="M100:N100"/>
+    <mergeCell ref="O29:O36"/>
+    <mergeCell ref="A49:A65"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="A66:A73"/>
+    <mergeCell ref="O37:O39"/>
+    <mergeCell ref="O40:O73"/>
+    <mergeCell ref="I37:J39"/>
+    <mergeCell ref="K37:L39"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="M84:N84"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="M91:N91"/>
+    <mergeCell ref="M92:N92"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="A29:A36"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="A77:A85"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="M69:N69"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="M71:N71"/>
+    <mergeCell ref="M95:N95"/>
+    <mergeCell ref="M96:N96"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="M82:N82"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="M72:N72"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="M67:N67"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="M61:N61"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="M37:N39"/>
+    <mergeCell ref="O26:O28"/>
+    <mergeCell ref="M26:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="K82:L82"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="K74:L76"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="F194:G194"/>
+    <mergeCell ref="F195:G195"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="G168:H168"/>
+    <mergeCell ref="E175:F175"/>
+    <mergeCell ref="G175:H175"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="G176:H176"/>
+    <mergeCell ref="E177:F177"/>
+    <mergeCell ref="G177:H177"/>
+    <mergeCell ref="E178:F178"/>
+    <mergeCell ref="G178:H178"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="G172:H172"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="H193:I193"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="I26:J28"/>
+    <mergeCell ref="K26:L28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="A161:A168"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="B167:C167"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="B166:C166"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="J193:K193"/>
+    <mergeCell ref="L193:M193"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="H194:I194"/>
+    <mergeCell ref="J194:K194"/>
+    <mergeCell ref="L194:M194"/>
+    <mergeCell ref="G160:H160"/>
+    <mergeCell ref="B187:C187"/>
+    <mergeCell ref="E187:F187"/>
+    <mergeCell ref="G187:H187"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="E182:F182"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="E183:F183"/>
+    <mergeCell ref="G183:H183"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="E173:F173"/>
+    <mergeCell ref="E156:F156"/>
+    <mergeCell ref="G156:H156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="G157:H157"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="A153:A160"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="G158:H158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="G159:H159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="A150:A152"/>
+    <mergeCell ref="B150:C152"/>
+    <mergeCell ref="D150:D152"/>
+    <mergeCell ref="E150:F152"/>
+    <mergeCell ref="G150:H152"/>
+    <mergeCell ref="I150:I152"/>
+    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="A132:A139"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="A141:M141"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A143:B143"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G37:H39"/>
+    <mergeCell ref="G26:H28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="E26:F28"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="B26:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="A86:A102"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="H107:H109"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="G96:H96"/>
     <mergeCell ref="A208:B208"/>
     <mergeCell ref="E208:F208"/>
     <mergeCell ref="H208:I208"/>
@@ -10419,699 +11103,6 @@
     <mergeCell ref="B102:C102"/>
     <mergeCell ref="E102:F102"/>
     <mergeCell ref="G102:H102"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="H107:H109"/>
-    <mergeCell ref="G92:H92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="A86:A102"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="E26:F28"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="B26:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G37:H39"/>
-    <mergeCell ref="G26:H28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="E37:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="A141:M141"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="A132:A139"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:H72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="A150:A152"/>
-    <mergeCell ref="B150:C152"/>
-    <mergeCell ref="D150:D152"/>
-    <mergeCell ref="E150:F152"/>
-    <mergeCell ref="G150:H152"/>
-    <mergeCell ref="I150:I152"/>
-    <mergeCell ref="A144:B144"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="E156:F156"/>
-    <mergeCell ref="G156:H156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="E157:F157"/>
-    <mergeCell ref="G157:H157"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="E155:F155"/>
-    <mergeCell ref="A153:A160"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="E153:F153"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="E158:F158"/>
-    <mergeCell ref="G158:H158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="G159:H159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="E160:F160"/>
-    <mergeCell ref="J193:K193"/>
-    <mergeCell ref="L193:M193"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="H194:I194"/>
-    <mergeCell ref="J194:K194"/>
-    <mergeCell ref="L194:M194"/>
-    <mergeCell ref="G160:H160"/>
-    <mergeCell ref="B187:C187"/>
-    <mergeCell ref="E187:F187"/>
-    <mergeCell ref="G187:H187"/>
-    <mergeCell ref="B182:C182"/>
-    <mergeCell ref="E182:F182"/>
-    <mergeCell ref="G182:H182"/>
-    <mergeCell ref="B183:C183"/>
-    <mergeCell ref="E183:F183"/>
-    <mergeCell ref="G183:H183"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="E169:F169"/>
-    <mergeCell ref="G169:H169"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="G171:H171"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="B173:C173"/>
-    <mergeCell ref="E173:F173"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="A161:A168"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="E161:F161"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="E164:F164"/>
-    <mergeCell ref="B167:C167"/>
-    <mergeCell ref="E167:F167"/>
-    <mergeCell ref="G161:H161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="E162:F162"/>
-    <mergeCell ref="G162:H162"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="G164:H164"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="E165:F165"/>
-    <mergeCell ref="G165:H165"/>
-    <mergeCell ref="B166:C166"/>
-    <mergeCell ref="E166:F166"/>
-    <mergeCell ref="G166:H166"/>
-    <mergeCell ref="G167:H167"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="E168:F168"/>
-    <mergeCell ref="I26:J28"/>
-    <mergeCell ref="K26:L28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="F194:G194"/>
-    <mergeCell ref="F195:G195"/>
-    <mergeCell ref="F196:G196"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="F199:G199"/>
-    <mergeCell ref="F200:G200"/>
-    <mergeCell ref="G168:H168"/>
-    <mergeCell ref="E175:F175"/>
-    <mergeCell ref="G175:H175"/>
-    <mergeCell ref="E176:F176"/>
-    <mergeCell ref="G176:H176"/>
-    <mergeCell ref="E177:F177"/>
-    <mergeCell ref="G177:H177"/>
-    <mergeCell ref="E178:F178"/>
-    <mergeCell ref="G178:H178"/>
-    <mergeCell ref="E179:F179"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="F193:G193"/>
-    <mergeCell ref="H193:I193"/>
-    <mergeCell ref="G173:H173"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="K74:L76"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="K82:L82"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="M37:N39"/>
-    <mergeCell ref="O26:O28"/>
-    <mergeCell ref="M26:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="I100:J100"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="M61:N61"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A7:O7"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="M55:N55"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="A29:A36"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="A77:A85"/>
-    <mergeCell ref="M68:N68"/>
-    <mergeCell ref="M69:N69"/>
-    <mergeCell ref="M70:N70"/>
-    <mergeCell ref="M71:N71"/>
-    <mergeCell ref="M95:N95"/>
-    <mergeCell ref="M96:N96"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="M81:N81"/>
-    <mergeCell ref="M82:N82"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="M72:N72"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="M67:N67"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="M58:N58"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="I74:J76"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="M100:N100"/>
-    <mergeCell ref="O29:O36"/>
-    <mergeCell ref="A49:A65"/>
-    <mergeCell ref="M62:N62"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="A66:A73"/>
-    <mergeCell ref="O37:O39"/>
-    <mergeCell ref="O40:O73"/>
-    <mergeCell ref="I37:J39"/>
-    <mergeCell ref="K37:L39"/>
-    <mergeCell ref="M83:N83"/>
-    <mergeCell ref="M84:N84"/>
-    <mergeCell ref="M85:N85"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="M87:N87"/>
-    <mergeCell ref="M91:N91"/>
-    <mergeCell ref="M92:N92"/>
-    <mergeCell ref="M93:N93"/>
-    <mergeCell ref="B74:C76"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="E74:F76"/>
-    <mergeCell ref="G74:H76"/>
-    <mergeCell ref="L150:M152"/>
-    <mergeCell ref="M98:N98"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="O74:O76"/>
-    <mergeCell ref="O77:O102"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="M94:N94"/>
-    <mergeCell ref="M97:N97"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="J153:K153"/>
-    <mergeCell ref="L153:M153"/>
-    <mergeCell ref="J154:K154"/>
-    <mergeCell ref="L154:M154"/>
-    <mergeCell ref="J155:K155"/>
-    <mergeCell ref="L155:M155"/>
-    <mergeCell ref="H111:H139"/>
-    <mergeCell ref="J150:K152"/>
-    <mergeCell ref="M74:N76"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="J159:K159"/>
-    <mergeCell ref="L159:M159"/>
-    <mergeCell ref="J160:K160"/>
-    <mergeCell ref="L160:M160"/>
-    <mergeCell ref="J161:K161"/>
-    <mergeCell ref="L161:M161"/>
-    <mergeCell ref="J156:K156"/>
-    <mergeCell ref="L156:M156"/>
-    <mergeCell ref="J157:K157"/>
-    <mergeCell ref="L157:M157"/>
-    <mergeCell ref="J158:K158"/>
-    <mergeCell ref="L158:M158"/>
-    <mergeCell ref="J165:K165"/>
-    <mergeCell ref="L165:M165"/>
-    <mergeCell ref="J166:K166"/>
-    <mergeCell ref="L166:M166"/>
-    <mergeCell ref="J167:K167"/>
-    <mergeCell ref="L167:M167"/>
-    <mergeCell ref="J162:K162"/>
-    <mergeCell ref="L162:M162"/>
-    <mergeCell ref="J163:K163"/>
-    <mergeCell ref="L163:M163"/>
-    <mergeCell ref="J164:K164"/>
-    <mergeCell ref="L164:M164"/>
-    <mergeCell ref="J171:K171"/>
-    <mergeCell ref="L171:M171"/>
-    <mergeCell ref="J172:K172"/>
-    <mergeCell ref="L172:M172"/>
-    <mergeCell ref="J173:K173"/>
-    <mergeCell ref="L173:M173"/>
-    <mergeCell ref="J168:K168"/>
-    <mergeCell ref="L168:M168"/>
-    <mergeCell ref="J169:K169"/>
-    <mergeCell ref="L169:M169"/>
-    <mergeCell ref="J170:K170"/>
-    <mergeCell ref="L170:M170"/>
-    <mergeCell ref="L177:M177"/>
-    <mergeCell ref="J178:K178"/>
-    <mergeCell ref="L178:M178"/>
-    <mergeCell ref="J174:K174"/>
-    <mergeCell ref="L174:M174"/>
-    <mergeCell ref="J175:K175"/>
-    <mergeCell ref="L175:M175"/>
-    <mergeCell ref="A177:A183"/>
-    <mergeCell ref="A184:A186"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="E174:F174"/>
-    <mergeCell ref="G174:H174"/>
-    <mergeCell ref="B175:C175"/>
-    <mergeCell ref="B176:C176"/>
-    <mergeCell ref="B177:C177"/>
-    <mergeCell ref="B178:C178"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="G179:H179"/>
-    <mergeCell ref="B180:C180"/>
-    <mergeCell ref="E180:F180"/>
-    <mergeCell ref="G180:H180"/>
-    <mergeCell ref="B181:C181"/>
-    <mergeCell ref="E181:F181"/>
-    <mergeCell ref="G181:H181"/>
-    <mergeCell ref="J187:K187"/>
-    <mergeCell ref="L187:M187"/>
-    <mergeCell ref="J184:K186"/>
-    <mergeCell ref="L184:M186"/>
-    <mergeCell ref="J179:K179"/>
-    <mergeCell ref="L179:M179"/>
-    <mergeCell ref="J180:K180"/>
-    <mergeCell ref="L180:M180"/>
-    <mergeCell ref="J181:K181"/>
-    <mergeCell ref="L181:M181"/>
-    <mergeCell ref="A16:P16"/>
-    <mergeCell ref="A169:A176"/>
-    <mergeCell ref="B184:C186"/>
-    <mergeCell ref="D184:D186"/>
-    <mergeCell ref="E184:F186"/>
-    <mergeCell ref="G184:H186"/>
-    <mergeCell ref="I184:I186"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="E170:F170"/>
-    <mergeCell ref="G170:H170"/>
-    <mergeCell ref="N184:N186"/>
-    <mergeCell ref="O150:O152"/>
-    <mergeCell ref="P150:P152"/>
-    <mergeCell ref="N150:N152"/>
-    <mergeCell ref="O184:O186"/>
-    <mergeCell ref="P184:P186"/>
-    <mergeCell ref="P153:P183"/>
-    <mergeCell ref="J182:K182"/>
-    <mergeCell ref="L182:M182"/>
-    <mergeCell ref="J183:K183"/>
-    <mergeCell ref="L183:M183"/>
-    <mergeCell ref="J176:K176"/>
-    <mergeCell ref="L176:M176"/>
-    <mergeCell ref="J177:K177"/>
-    <mergeCell ref="A191:C193"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="H197:I197"/>
-    <mergeCell ref="J197:K197"/>
-    <mergeCell ref="L197:M197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="H198:I198"/>
-    <mergeCell ref="J198:K198"/>
-    <mergeCell ref="L198:M198"/>
-    <mergeCell ref="H195:I195"/>
-    <mergeCell ref="J195:K195"/>
-    <mergeCell ref="L195:M195"/>
-    <mergeCell ref="A196:C196"/>
-    <mergeCell ref="H196:I196"/>
-    <mergeCell ref="J196:K196"/>
-    <mergeCell ref="L196:M196"/>
-    <mergeCell ref="A195:C195"/>
-    <mergeCell ref="D196:E196"/>
-    <mergeCell ref="D197:E197"/>
-    <mergeCell ref="D198:E198"/>
-    <mergeCell ref="D191:E193"/>
-    <mergeCell ref="D194:E194"/>
-    <mergeCell ref="D195:E195"/>
-    <mergeCell ref="F191:M192"/>
-    <mergeCell ref="A201:C201"/>
-    <mergeCell ref="H201:I201"/>
-    <mergeCell ref="J201:K201"/>
-    <mergeCell ref="L201:M201"/>
-    <mergeCell ref="A199:C199"/>
-    <mergeCell ref="H199:I199"/>
-    <mergeCell ref="J199:K199"/>
-    <mergeCell ref="L199:M199"/>
-    <mergeCell ref="A200:C200"/>
-    <mergeCell ref="H200:I200"/>
-    <mergeCell ref="J200:K200"/>
-    <mergeCell ref="L200:M200"/>
-    <mergeCell ref="D199:E199"/>
-    <mergeCell ref="D200:E200"/>
-    <mergeCell ref="D201:E201"/>
-    <mergeCell ref="F201:G201"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.59055118110236227" bottom="0.59055118110236227" header="0.51181102362204722" footer="0.31496062992125984"/>
